--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,26 +503,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Assurance and Compliance</t>
+          <t>HMGCC Co-Creation Challenge: Multi-Terrain Micro Robotic Systems</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2597/overview/7ec02a95-73e5-4928-8104-67a9f1b279e3</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/hmgcc-co-creation-challenge-multi-terrain-micro-robotic-systems/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-06 16:27</t>
+          <t>2026-10-12 19:27</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301.68541666667</v>
+        <v>46307.81041666667</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -531,48 +531,52 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46307</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Tuesday 8 December 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>46364.45833333334</v>
-      </c>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Decision Critical Systems</t>
+          <t>HMGCC Co-Creation Challenge: Smart glasses for mapping</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2598/overview/cfb35198-55fc-4aad-afa1-86a260bfaddf</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/hmgcc-co-creation-challenge-smart-glasses-for-mapping/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:27</t>
+          <t>2026-10-12 19:27</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301.68541666667</v>
+        <v>46307.81041666667</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -581,29 +585,33 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>46307</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Tuesday 8 December 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>46364.45833333334</v>
-      </c>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -613,16 +621,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2599/overview/1931f35c-87fe-4b6a-a718-a61a2d00e86a</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/bridgeai-deployment-catalyst-ai-for-operational-systems/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-06 16:27</t>
+          <t>2026-10-10 15:37</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301.68541666667</v>
+        <v>46305.65069444444</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -631,11 +639,17 @@
       <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>46316</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Tuesday 8 December 2026 11:00am</t>
+          <t>08/12/2026                              11:00</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
@@ -643,11 +657,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£52.0 million</t>
         </is>
       </c>
       <c r="N4" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="5">
@@ -658,21 +672,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eureka collaborative R&amp;D: Globalstars Japan 2027</t>
+          <t>BridgeAI Deployment Catalyst: AI for Decision Critical Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/eureka-collaborative-rd-globalstars-japan-2027/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/bridgeai-deployment-catalyst-ai-for-decision-critical-systems/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-06 16:20</t>
+          <t>2026-10-10 15:37</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301.68055555555</v>
+        <v>46305.65069444444</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -683,27 +697,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>08/12/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>46364.45833333334</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>£52.0 million</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="n">
         <v>46302</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>20/01/2027                              11:00</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>46407.45833333334</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>£2.0 million</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>46295</v>
       </c>
     </row>
     <row r="6">
@@ -714,21 +728,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Next Wave: Global Business Innovation Programme – Createch South by Southwest (SXSW), Texas</t>
+          <t>BridgeAI Deployment Catalyst: AI for Assurance and Compliance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/next-wave-gbip-createch-sxsw-texas/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/bridgeai-deployment-catalyst-ai-for-assurance-and-compliance/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-06 16:20</t>
+          <t>2026-10-10 15:37</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301.68055555555</v>
+        <v>46305.65069444444</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -739,21 +753,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>46301</v>
+        <v>46316</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>08/12/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>46364.45833333334</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>£52.0 million</t>
+        </is>
+      </c>
       <c r="N6" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="7">
@@ -764,21 +784,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 12</t>
+          <t>iX Challenge: Accelerating Digital Engineering Through MBSE Simulation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/adopt-facilitator-support-grant-round-12/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-accelerating-digital-engineering-through-mbse-simulation/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-06 16:20</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301.68055555555</v>
+        <v>46304.69375</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -789,27 +809,25 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11/11/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>46337.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N7" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="8">
@@ -820,21 +838,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iX Challenge: AI Attribution and AI Authenticity for Ethical Cultural Content</t>
+          <t>Full ADOPT Grant: Round 10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-ai-attribution-and-ai-authenticity-for-ethical-cultural-content/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/full-adopt-grant-round-10/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-06 16:20</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301.68055555555</v>
+        <v>46304.69375</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -845,25 +863,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13/11/2026</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>02/12/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>46358.45833333334</v>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N8" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="9">
@@ -874,21 +894,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Investor Partnerships – Battery Innovation Programme</t>
+          <t>iX Challenge: Repeatable Adversarial Evaluation of Physical Tamper Protection for Defence Electronics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/investor-partnerships-battery-innovation-programme/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-repeatable-adversarial-evaluation-of-physical-tamper-protection-for-defence-electronics/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-06 16:20</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301.68055555555</v>
+        <v>46304.69375</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -899,52 +919,50 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25/11/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>46351.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N9" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sustainable Medicines Manufacturing Innovation: CR&amp;D Round 2</t>
+          <t>Full ADOPT Grant: Round 10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/sustainable-medicines-manufacturing-innovation-crd-round-2/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2596/overview/31f0a768-2a9a-405d-b0a4-83a8c5b395c0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-06 16:20</t>
+          <t>2026-10-08 17:07</t>
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301.68055555555</v>
+        <v>46303.71319444444</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -953,17 +971,11 @@
       <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>46300</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>02/12/2026                              11:00</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L10" s="1" t="n">
@@ -971,36 +983,36 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>£7.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N10" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eureka collaborative R&amp;D: Globalstars Japan 2027</t>
+          <t>iX Challenge: Reducing blood-cell loss and measurement variability in field-deployable microfluidic diagnostic cartridges</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2586/overview/d9e61ae4-6e56-4f38-9206-5d91ef98c916</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-reducing-blood-cell-loss-and-measurement-variability-in-field-deployable-microfluidic-diagnostic-cartridges/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-05 19:06</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300.79583333333</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -1009,48 +1021,54 @@
       <c r="H11" t="b">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>46300</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Wednesday 20 January 2027 11:00am</t>
+          <t>06/11/2026                              11:00</t>
         </is>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46407.45833333334</v>
+        <v>46332.45833333334</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N11" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sustainable Medicines Manufacturing Innovation: CR&amp;D Round 2</t>
+          <t>FOAK Builder: working towards climate tech first-of-a-kind deployment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2560/overview/45acacd5-746b-46ee-8051-d764f929cca3</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/foak-builder-working-towards-climate-tech-first-of-a-kind-deployment/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-05 19:06</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300.79583333333</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -1059,48 +1077,54 @@
       <c r="H12" t="b">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>46302</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>05/11/2026                              11:00</t>
         </is>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46331.45833333334</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£4.8 million</t>
         </is>
       </c>
       <c r="N12" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Investor Partnerships – Battery Innovation Programme</t>
+          <t>iX Challenge: Verified reporting of the value created by defence contracts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2595/overview/f2b849f6-0fb3-4012-be1b-a41813c93085</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-verified-reporting-of-the-value-created-by-defence-contracts/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-05 19:06</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300.79583333333</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -1109,48 +1133,52 @@
       <c r="H13" t="b">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>46300</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Wednesday 25 November 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>46351.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N13" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 12</t>
+          <t>iX Challenge: Extending protection to personnel travelling in armoured vehicles under drone attack</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2591/overview/b66dd413-9894-4fc4-a6c9-cced53367568</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-extending-protection-to-personnel-travelling-in-armoured-vehicles-under-drone-attack/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-05 19:06</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300.79583333333</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -1159,23 +1187,27 @@
       <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>46300</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Wednesday 11 November 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>46337.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N14" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="15">
@@ -1186,21 +1218,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HMGCC Co-Creation Challenge: Hidden stab vests for women</t>
+          <t>iX Challenge: Edge AI with Low Size, Weight, Power, and Cost</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/hmgcc-co-creation-challenge-hidden-stab-vests-for-women/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-edge-ai-with-low-size-weight-power-and-cost/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-05 18:54</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300.7875</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -1219,19 +1251,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>05/11/2026                              12:00</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>46331.5</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>£60,000</t>
         </is>
       </c>
       <c r="N15" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="16">
@@ -1242,21 +1272,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Engineering Biology Investor Partnerships Round 1</t>
+          <t>iX Challenge: Resilient High-Altitude Communications, Navigation and Mission Connectivity for Persistent Autonomous Aircraft</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/engineering-biology-investor-partnerships-round-1/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-resilient-high-altitude-communications-navigation-and-mission-connectivity-for-persistent-autonomous-aircraft/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-05 18:54</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300.7875</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -1267,27 +1297,25 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02/12/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>46358.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N16" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="17">
@@ -1298,21 +1326,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manufacturing Digitalisation Innovation Programme: Innovation and Scale-up Hub</t>
+          <t>iX Challenge: Distributed Smartphone-Based Detection and Mapping of PNT Signal Interference</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/mdi-programme-innovation-and-scale-up-hub/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-distributed-smartphone-based-detection-and-mapping-of-pnt-signal-interference/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-05 18:54</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300.7875</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -1323,52 +1351,50 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18/11/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>46344.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>£175.0 million</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N17" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MDI Programme Innovation and Scale-up Hub</t>
+          <t>iX Challenge: Secure, Cost-Effective Use of Cloud-Based AI Tools in the Defence Supply Chain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2588/overview/acbd9666-c1df-4635-b86f-fa426100c876</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-secure-cost-effective-use-of-cloud-based-ai-tools-in-the-defence-supply-chain/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-03 14:31</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298.60486111111</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -1377,48 +1403,52 @@
       <c r="H18" t="b">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>46300</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Wednesday 18 November 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="n">
-        <v>46344.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N18" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Engineering Biology Investor Partnerships Round 1</t>
+          <t>iX Challenge: Next-Generation Electronics for UK Bathymetric Sonar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2580/overview/8881af18-31f4-4db3-9483-cbb047163164</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-next-generation-electronics-for-uk-bathymetric-sonar/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-01 16:50</t>
+          <t>2026-10-08 17:01</t>
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296.70138888889</v>
+        <v>46303.70902777778</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -1427,48 +1457,52 @@
       <c r="H19" t="b">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>46302</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>46358.45833333334</v>
-      </c>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60,000</t>
         </is>
       </c>
       <c r="N19" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UKAEA ICURe Engage - November 2026</t>
+          <t>FOAK Builder: Programme Entry Expression of Interest</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ukaea-icure-engage-november-2026/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2600/overview/0c422454-a8af-4c24-a74a-565426f42395</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-01 16:44</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296.69722222222</v>
+        <v>46302.71527777778</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -1477,81 +1511,23 @@
       <c r="H20" t="b">
         <v>0</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>02/10/2026</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>46297</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>29/10/2026                              11:59</t>
+          <t>Thursday 5 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46324.49930555555</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
+        <v>46331.45833333334</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>£100.0 million</t>
+        </is>
+      </c>
       <c r="N20" s="1" t="n">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>UK Defence Innovation: Security Open Call 2026 Cycle 2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/uk-defence-innovation-security-open-call-2026-cycle-2/</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-10-01 16:44</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46296.69722222222</v>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>29/10/2026                              12:00</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="n">
-        <v>46324.5</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>£350,000</t>
-        </is>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
     </row>
   </sheetData>
@@ -1565,7 +1541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,26 +1619,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMGCC Co-Creation Challenge: Multi-Terrain Micro Robotic Systems</t>
+          <t>Growth Cohorts: Next-gen low carbon concrete cohort entry Round 2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/hmgcc-co-creation-challenge-multi-terrain-micro-robotic-systems/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2602/overview/607351e2-798f-450b-b77d-3131912bcbef</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:27</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307.81041666667</v>
+        <v>46309.61805555555</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1671,1003 +1647,23 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46307</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12/11/2026</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Wednesday 2 December 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46358.45833333334</v>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£60,000</t>
+          <t>£54,400</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HMGCC Co-Creation Challenge: Smart glasses for mapping</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/hmgcc-co-creation-challenge-smart-glasses-for-mapping/</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:27</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46307.81041666667</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>12/11/2026</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BridgeAI Deployment Catalyst: AI for Operational Systems</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/bridgeai-deployment-catalyst-ai-for-operational-systems/</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-10-10 15:37</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46305.65069444444</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>08/12/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>46364.45833333334</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>£52.0 million</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BridgeAI Deployment Catalyst: AI for Decision Critical Systems</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/bridgeai-deployment-catalyst-ai-for-decision-critical-systems/</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-10-10 15:37</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46305.65069444444</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>08/12/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>46364.45833333334</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>£52.0 million</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BridgeAI Deployment Catalyst: AI for Assurance and Compliance</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/bridgeai-deployment-catalyst-ai-for-assurance-and-compliance/</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-10-10 15:37</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46305.65069444444</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21/10/2026</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>08/12/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>46364.45833333334</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>£52.0 million</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>iX Challenge: Accelerating Digital Engineering Through MBSE Simulation</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-accelerating-digital-engineering-through-mbse-simulation/</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-10-09 16:39</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46304.69375</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Full ADOPT Grant: Round 10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/full-adopt-grant-round-10/</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-10-09 16:39</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46304.69375</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>08/10/2026</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>02/12/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>46358.45833333334</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>£5.0 million</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>iX Challenge: Repeatable Adversarial Evaluation of Physical Tamper Protection for Defence Electronics</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-repeatable-adversarial-evaluation-of-physical-tamper-protection-for-defence-electronics/</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-10-09 16:39</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46304.69375</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Innovate Funding Service</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Full ADOPT Grant: Round 10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2596/overview/31f0a768-2a9a-405d-b0a4-83a8c5b395c0</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:07</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46303.71319444444</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>46358.45833333334</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>£200,000</t>
-        </is>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>iX Challenge: Reducing blood-cell loss and measurement variability in field-deployable microfluidic diagnostic cartridges</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-reducing-blood-cell-loss-and-measurement-variability-in-field-deployable-microfluidic-diagnostic-cartridges/</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>06/11/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>46332.45833333334</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FOAK Builder: working towards climate tech first-of-a-kind deployment</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/foak-builder-working-towards-climate-tech-first-of-a-kind-deployment/</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>05/11/2026                              11:00</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>46331.45833333334</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>£4.8 million</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>iX Challenge: Verified reporting of the value created by defence contracts</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-verified-reporting-of-the-value-created-by-defence-contracts/</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>iX Challenge: Extending protection to personnel travelling in armoured vehicles under drone attack</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-extending-protection-to-personnel-travelling-in-armoured-vehicles-under-drone-attack/</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>iX Challenge: Edge AI with Low Size, Weight, Power, and Cost</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-edge-ai-with-low-size-weight-power-and-cost/</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>iX Challenge: Resilient High-Altitude Communications, Navigation and Mission Connectivity for Persistent Autonomous Aircraft</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-resilient-high-altitude-communications-navigation-and-mission-connectivity-for-persistent-autonomous-aircraft/</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>iX Challenge: Distributed Smartphone-Based Detection and Mapping of PNT Signal Interference</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-distributed-smartphone-based-detection-and-mapping-of-pnt-signal-interference/</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>iX Challenge: Secure, Cost-Effective Use of Cloud-Based AI Tools in the Defence Supply Chain</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-secure-cost-effective-use-of-cloud-based-ai-tools-in-the-defence-supply-chain/</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Innovate UK Business Connect</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>iX Challenge: Next-Generation Electronics for UK Bathymetric Sonar</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-next-generation-electronics-for-uk-bathymetric-sonar/</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:01</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46303.70902777778</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>06/11/2026</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>£60,000</t>
-        </is>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Innovate Funding Service</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FOAK Builder: Programme Entry Expression of Interest</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2600/overview/0c422454-a8af-4c24-a74a-565426f42395</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-10-07 17:10</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46302.71527777778</v>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Thursday 5 November 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="n">
-        <v>46331.45833333334</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>£100.0 million</t>
-        </is>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
     </row>
   </sheetData>
@@ -2681,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2708,83 +1704,83 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
@@ -2792,189 +1788,189 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46183</v>
+        <v>46190</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="B21" t="n">
         <v>5</v>
@@ -2988,385 +1984,385 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
-        <v>9</v>
-      </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46071</v>
+        <v>46078</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
         <v>9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46008</v>
+        <v>46015</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45994</v>
+        <v>46001</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45980</v>
+        <v>45987</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45973</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
@@ -3380,91 +2376,91 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45966</v>
+        <v>45973</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45959</v>
+        <v>45966</v>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="B52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45938</v>
+        <v>45945</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45931</v>
+        <v>45938</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45924</v>
+        <v>45931</v>
       </c>
       <c r="B56" t="n">
         <v>1</v>
@@ -3478,35 +2474,35 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45910</v>
+        <v>45917</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45903</v>
+        <v>45910</v>
       </c>
       <c r="B59" t="n">
         <v>2</v>
@@ -3520,169 +2516,183 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45882</v>
+        <v>45889</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45875</v>
+        <v>45882</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45868</v>
+        <v>45875</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45861</v>
+        <v>45868</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45854</v>
+        <v>45861</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45847</v>
+        <v>45854</v>
       </c>
       <c r="B67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45840</v>
+        <v>45847</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45833</v>
+        <v>45840</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45826</v>
+        <v>45833</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
         <v>45819</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B72" t="n">
         <v>25</v>
       </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3697,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N730"/>
+  <dimension ref="A1:N731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40868,6 +39878,56 @@
       </c>
       <c r="N730" s="1" t="n">
         <v>46302</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Growth Cohorts: Next-gen low carbon concrete cohort entry Round 2</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2602/overview/607351e2-798f-450b-b77d-3131912bcbef</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:50</t>
+        </is>
+      </c>
+      <c r="E731" s="1" t="n">
+        <v>46309.61805555555</v>
+      </c>
+      <c r="F731" t="b">
+        <v>1</v>
+      </c>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="b">
+        <v>0</v>
+      </c>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Wednesday 2 December 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L731" s="1" t="n">
+        <v>46358.45833333334</v>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>£54,400</t>
+        </is>
+      </c>
+      <c r="N731" s="1" t="n">
+        <v>46309</v>
       </c>
     </row>
   </sheetData>
@@ -40921,10 +39981,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
@@ -40934,10 +39994,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C4" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,26 +1109,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
+          <t>Healthy Soils and Water for a Sustainable Environment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-21 14:43</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316.61319444444</v>
+        <v>46317.61736111111</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1137,23 +1137,19 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46314</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Thursday 28 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46415.45833333334</v>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
+          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1193,21 +1189,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1222,12 +1218,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1247,20 +1243,74 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:43</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46316.61319444444</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>01/12/2026</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" s="1" t="n">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="1" t="n">
         <v>46316</v>
       </c>
     </row>
@@ -1305,13 +1355,13 @@
         <v>46316</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2319,7 +2369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N743"/>
+  <dimension ref="A1:N744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40168,6 +40218,56 @@
       <c r="M743" t="inlineStr"/>
       <c r="N743" s="1" t="n">
         <v>46309</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Healthy Soils and Water for a Sustainable Environment</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:49</t>
+        </is>
+      </c>
+      <c r="E744" s="1" t="n">
+        <v>46317.61736111111</v>
+      </c>
+      <c r="F744" t="b">
+        <v>1</v>
+      </c>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="b">
+        <v>0</v>
+      </c>
+      <c r="I744" t="inlineStr"/>
+      <c r="J744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Thursday 28 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L744" s="1" t="n">
+        <v>46415.45833333334</v>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
+      <c r="N744" s="1" t="n">
+        <v>46316</v>
       </c>
     </row>
   </sheetData>
@@ -40221,10 +40321,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -40234,10 +40334,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C4" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,26 +1109,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Healthy Soils and Water for a Sustainable Environment</t>
+          <t>Secure Innovation Security Reviews</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/secure-innovation-security-review/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:29</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317.61736111111</v>
+        <v>46318.60347222222</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1137,19 +1137,25 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46318</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Thursday 28 January 2027 11:00am</t>
+          <t>31/01/2027                              12:00</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46415.45833333334</v>
+        <v>46418.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£315,000</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
@@ -1159,26 +1165,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
+          <t>Healthy Soils and Water for a Sustainable Environment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:43</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316.61319444444</v>
+        <v>46317.61736111111</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1187,23 +1193,19 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46314</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Thursday 28 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>46415.45833333334</v>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1218,12 +1220,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
+          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1243,21 +1245,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N4" s="1" t="n">
@@ -1272,12 +1274,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1297,20 +1299,74 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:43</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46316.61319444444</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>01/12/2026</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" s="1" t="n">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="1" t="n">
         <v>46316</v>
       </c>
     </row>
@@ -1358,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2369,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N744"/>
+  <dimension ref="A1:N745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28045,26 +28101,26 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>Secure Innovation Security Reviews</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/secure-innovation-security-review/</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-10-23 14:29</t>
         </is>
       </c>
       <c r="E499" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46318.60347222222</v>
       </c>
       <c r="F499" t="b">
         <v>1</v>
@@ -28073,23 +28129,29 @@
       <c r="H499" t="b">
         <v>0</v>
       </c>
-      <c r="I499" t="inlineStr"/>
-      <c r="J499" t="inlineStr"/>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="J499" s="1" t="n">
+        <v>46318</v>
+      </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>31/01/2027                              12:00</t>
         </is>
       </c>
       <c r="L499" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46418.5</v>
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£315,000</t>
         </is>
       </c>
       <c r="N499" s="1" t="n">
-        <v>45819</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="500">
@@ -28100,12 +28162,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -28127,15 +28189,15 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L500" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N500" s="1" t="n">
@@ -28150,12 +28212,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -28177,15 +28239,15 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L501" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N501" s="1" t="n">
@@ -28200,12 +28262,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -28235,7 +28297,7 @@
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N502" s="1" t="n">
@@ -28250,12 +28312,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -28277,15 +28339,15 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L503" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N503" s="1" t="n">
@@ -28300,12 +28362,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -28327,13 +28389,17 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L504" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M504" t="inlineStr"/>
+        <v>45904.45833333334</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N504" s="1" t="n">
         <v>45819</v>
       </c>
@@ -28346,12 +28412,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -28373,17 +28439,13 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L505" s="1" t="n">
-        <v>45840.45833333334</v>
-      </c>
-      <c r="M505" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M505" t="inlineStr"/>
       <c r="N505" s="1" t="n">
         <v>45819</v>
       </c>
@@ -28396,12 +28458,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -28423,15 +28485,15 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L506" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M506" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N506" s="1" t="n">
@@ -28446,12 +28508,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -28496,12 +28558,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -28523,15 +28585,15 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L508" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N508" s="1" t="n">
@@ -28546,12 +28608,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -28573,15 +28635,15 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L509" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N509" s="1" t="n">
@@ -28596,12 +28658,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -28623,15 +28685,15 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L510" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N510" s="1" t="n">
@@ -28646,12 +28708,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -28696,12 +28758,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -28723,15 +28785,15 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L512" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M512" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N512" s="1" t="n">
@@ -28746,12 +28808,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -28781,7 +28843,7 @@
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N513" s="1" t="n">
@@ -28796,12 +28858,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -28823,15 +28885,15 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L514" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N514" s="1" t="n">
@@ -28846,12 +28908,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -28873,15 +28935,15 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L515" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N515" s="1" t="n">
@@ -28896,12 +28958,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -28931,7 +28993,7 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N516" s="1" t="n">
@@ -28946,12 +29008,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -28973,15 +29035,15 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L517" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N517" s="1" t="n">
@@ -28996,12 +29058,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -29046,12 +29108,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -29073,15 +29135,15 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L519" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N519" s="1" t="n">
@@ -29096,12 +29158,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -29123,15 +29185,15 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L520" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N520" s="1" t="n">
@@ -29146,12 +29208,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -29173,11 +29235,17 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L521" t="inlineStr"/>
-      <c r="M521" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L521" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N521" s="1" t="n">
         <v>45819</v>
       </c>
@@ -29190,12 +29258,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -29234,21 +29302,21 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E523" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F523" t="b">
         <v>1</v>
@@ -29261,17 +29329,11 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L523" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M523" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
       <c r="N523" s="1" t="n">
         <v>45819</v>
       </c>
@@ -29284,21 +29346,21 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E524" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F524" t="b">
         <v>1</v>
@@ -29311,19 +29373,19 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L524" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N524" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="525">
@@ -29334,12 +29396,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -29369,7 +29431,7 @@
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N525" s="1" t="n">
@@ -29384,21 +29446,21 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E526" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F526" t="b">
         <v>1</v>
@@ -29411,19 +29473,19 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L526" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N526" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="527">
@@ -29434,21 +29496,21 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E527" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F527" t="b">
         <v>1</v>
@@ -29461,15 +29523,15 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L527" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N527" s="1" t="n">
@@ -29484,12 +29546,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -29511,13 +29573,17 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L528" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M528" t="inlineStr"/>
+        <v>45875.45833333334</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N528" s="1" t="n">
         <v>45840</v>
       </c>
@@ -29530,21 +29596,21 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E529" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F529" t="b">
         <v>1</v>
@@ -29557,19 +29623,15 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L529" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M529" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M529" t="inlineStr"/>
       <c r="N529" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="530">
@@ -29580,12 +29642,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -29630,12 +29692,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -29680,12 +29742,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -29707,15 +29769,15 @@
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L532" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N532" s="1" t="n">
@@ -29730,21 +29792,21 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E533" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F533" t="b">
         <v>1</v>
@@ -29757,15 +29819,15 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L533" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N533" s="1" t="n">
@@ -29780,12 +29842,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -29807,15 +29869,15 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L534" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M534" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N534" s="1" t="n">
@@ -29830,12 +29892,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -29865,7 +29927,7 @@
       </c>
       <c r="M535" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N535" s="1" t="n">
@@ -29880,21 +29942,21 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E536" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F536" t="b">
         <v>1</v>
@@ -29907,19 +29969,19 @@
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L536" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N536" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="537">
@@ -29930,21 +29992,21 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E537" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F537" t="b">
         <v>1</v>
@@ -29957,19 +30019,19 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L537" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M537" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N537" s="1" t="n">
-        <v>45875</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="538">
@@ -29980,21 +30042,21 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E538" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F538" t="b">
         <v>1</v>
@@ -30007,19 +30069,19 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L538" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N538" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="539">
@@ -30030,12 +30092,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -30065,7 +30127,7 @@
       </c>
       <c r="M539" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N539" s="1" t="n">
@@ -30080,12 +30142,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -30115,7 +30177,7 @@
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N540" s="1" t="n">
@@ -30130,21 +30192,21 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E541" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F541" t="b">
         <v>1</v>
@@ -30157,19 +30219,19 @@
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L541" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N541" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="542">
@@ -30180,21 +30242,21 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E542" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F542" t="b">
         <v>1</v>
@@ -30207,11 +30269,11 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L542" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M542" t="inlineStr">
         <is>
@@ -30219,7 +30281,7 @@
         </is>
       </c>
       <c r="N542" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="543">
@@ -30230,21 +30292,21 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E543" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F543" t="b">
         <v>1</v>
@@ -30257,13 +30319,17 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L543" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M543" t="inlineStr"/>
+        <v>45945.45833333334</v>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N543" s="1" t="n">
         <v>45896</v>
       </c>
@@ -30276,21 +30342,21 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E544" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F544" t="b">
         <v>1</v>
@@ -30303,17 +30369,13 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L544" s="1" t="n">
-        <v>45966.45833333334</v>
-      </c>
-      <c r="M544" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M544" t="inlineStr"/>
       <c r="N544" s="1" t="n">
         <v>45896</v>
       </c>
@@ -30326,21 +30388,21 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E545" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F545" t="b">
         <v>1</v>
@@ -30353,19 +30415,19 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L545" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N545" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="546">
@@ -30376,21 +30438,21 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E546" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F546" t="b">
         <v>1</v>
@@ -30403,15 +30465,15 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L546" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N546" s="1" t="n">
@@ -30426,21 +30488,21 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E547" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F547" t="b">
         <v>1</v>
@@ -30453,19 +30515,19 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L547" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N547" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="548">
@@ -30476,21 +30538,21 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E548" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F548" t="b">
         <v>1</v>
@@ -30503,15 +30565,15 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Tuesday 28 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L548" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45958.45833333334</v>
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N548" s="1" t="n">
@@ -30526,21 +30588,21 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E549" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F549" t="b">
         <v>1</v>
@@ -30553,17 +30615,19 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L549" t="inlineStr"/>
+          <t>Wednesday 15 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L549" s="1" t="n">
+        <v>45945.45833333334</v>
+      </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N549" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="550">
@@ -30574,21 +30638,21 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E550" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F550" t="b">
         <v>1</v>
@@ -30601,15 +30665,13 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L550" s="1" t="n">
-        <v>45995.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr"/>
       <c r="M550" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N550" s="1" t="n">
@@ -30624,21 +30686,21 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E551" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F551" t="b">
         <v>1</v>
@@ -30651,15 +30713,15 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L551" s="1" t="n">
-        <v>45964.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N551" s="1" t="n">
@@ -30674,21 +30736,21 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E552" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F552" t="b">
         <v>1</v>
@@ -30701,15 +30763,15 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L552" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N552" s="1" t="n">
@@ -30724,21 +30786,21 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E553" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F553" t="b">
         <v>1</v>
@@ -30751,19 +30813,19 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L553" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N553" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="554">
@@ -30774,21 +30836,21 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E554" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F554" t="b">
         <v>1</v>
@@ -30801,19 +30863,19 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L554" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N554" s="1" t="n">
-        <v>45931</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="555">
@@ -30824,21 +30886,21 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E555" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F555" t="b">
         <v>1</v>
@@ -30851,19 +30913,19 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L555" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46043.45833333334</v>
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N555" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="556">
@@ -30874,21 +30936,21 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E556" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F556" t="b">
         <v>1</v>
@@ -30901,13 +30963,17 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L556" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M556" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N556" s="1" t="n">
         <v>45938</v>
       </c>
@@ -30920,21 +30986,21 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E557" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F557" t="b">
         <v>1</v>
@@ -30947,19 +31013,15 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L557" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M557" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M557" t="inlineStr"/>
       <c r="N557" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="558">
@@ -30970,12 +31032,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -31005,7 +31067,7 @@
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N558" s="1" t="n">
@@ -31020,21 +31082,21 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E559" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F559" t="b">
         <v>1</v>
@@ -31047,15 +31109,15 @@
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L559" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N559" s="1" t="n">
@@ -31070,21 +31132,21 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E560" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F560" t="b">
         <v>1</v>
@@ -31105,7 +31167,7 @@
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N560" s="1" t="n">
@@ -31120,21 +31182,21 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E561" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F561" t="b">
         <v>1</v>
@@ -31147,15 +31209,15 @@
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L561" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N561" s="1" t="n">
@@ -31170,12 +31232,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -31205,7 +31267,7 @@
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N562" s="1" t="n">
@@ -31220,21 +31282,21 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E563" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F563" t="b">
         <v>1</v>
@@ -31247,13 +31309,17 @@
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L563" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M563" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N563" s="1" t="n">
         <v>45945</v>
       </c>
@@ -31266,21 +31332,21 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E564" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F564" t="b">
         <v>1</v>
@@ -31293,19 +31359,15 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L564" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M564" t="inlineStr">
-        <is>
-          <t>£1.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M564" t="inlineStr"/>
       <c r="N564" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="565">
@@ -31316,12 +31378,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -31351,7 +31413,7 @@
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N565" s="1" t="n">
@@ -31366,21 +31428,21 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E566" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F566" t="b">
         <v>1</v>
@@ -31401,7 +31463,7 @@
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N566" s="1" t="n">
@@ -31416,21 +31478,21 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E567" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F567" t="b">
         <v>1</v>
@@ -31443,15 +31505,15 @@
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L567" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N567" s="1" t="n">
@@ -31466,21 +31528,21 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E568" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F568" t="b">
         <v>1</v>
@@ -31493,15 +31555,15 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L568" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M568" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N568" s="1" t="n">
@@ -31516,21 +31578,21 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E569" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F569" t="b">
         <v>1</v>
@@ -31543,19 +31605,19 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L569" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N569" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="570">
@@ -31566,21 +31628,21 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E570" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F570" t="b">
         <v>1</v>
@@ -31593,15 +31655,15 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L570" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N570" s="1" t="n">
@@ -31616,12 +31678,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -31643,15 +31705,15 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L571" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M571" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N571" s="1" t="n">
@@ -31666,21 +31728,21 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E572" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F572" t="b">
         <v>1</v>
@@ -31693,19 +31755,19 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L572" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M572" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N572" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="573">
@@ -31716,12 +31778,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -31751,7 +31813,7 @@
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N573" s="1" t="n">
@@ -31766,12 +31828,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -31793,13 +31855,17 @@
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L574" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M574" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N574" s="1" t="n">
         <v>45966</v>
       </c>
@@ -31812,21 +31878,21 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E575" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F575" t="b">
         <v>1</v>
@@ -31839,17 +31905,13 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L575" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M575" t="inlineStr">
-        <is>
-          <t>£750,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M575" t="inlineStr"/>
       <c r="N575" s="1" t="n">
         <v>45966</v>
       </c>
@@ -31862,21 +31924,21 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E576" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F576" t="b">
         <v>1</v>
@@ -31889,19 +31951,19 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L576" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t>£75,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N576" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="577">
@@ -31912,21 +31974,21 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E577" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F577" t="b">
         <v>1</v>
@@ -31947,7 +32009,7 @@
       </c>
       <c r="M577" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N577" s="1" t="n">
@@ -31962,21 +32024,21 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F578" t="b">
         <v>1</v>
@@ -31989,19 +32051,19 @@
       <c r="J578" t="inlineStr"/>
       <c r="K578" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L578" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N578" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="579">
@@ -32012,21 +32074,21 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F579" t="b">
         <v>1</v>
@@ -32039,15 +32101,15 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L579" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M579" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N579" s="1" t="n">
@@ -32062,21 +32124,21 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F580" t="b">
         <v>1</v>
@@ -32089,19 +32151,19 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L580" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N580" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="581">
@@ -32112,12 +32174,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -32139,15 +32201,15 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L581" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M581" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N581" s="1" t="n">
@@ -32162,21 +32224,21 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F582" t="b">
         <v>1</v>
@@ -32189,19 +32251,19 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L582" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N582" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="583">
@@ -32212,12 +32274,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -32247,7 +32309,7 @@
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N583" s="1" t="n">
@@ -32262,12 +32324,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -32297,7 +32359,7 @@
       </c>
       <c r="M584" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N584" s="1" t="n">
@@ -32312,12 +32374,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -32339,15 +32401,15 @@
       <c r="J585" t="inlineStr"/>
       <c r="K585" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L585" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N585" s="1" t="n">
@@ -32362,12 +32424,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -32389,15 +32451,15 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L586" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M586" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N586" s="1" t="n">
@@ -32412,21 +32474,21 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F587" t="b">
         <v>1</v>
@@ -32439,19 +32501,19 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L587" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N587" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="588">
@@ -32462,21 +32524,21 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F588" t="b">
         <v>1</v>
@@ -32489,19 +32551,19 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L588" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N588" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="589">
@@ -32512,21 +32574,21 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46042.35</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F589" t="b">
         <v>1</v>
@@ -32539,15 +32601,15 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L589" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N589" s="1" t="n">
@@ -32562,21 +32624,21 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46042.35</v>
       </c>
       <c r="F590" t="b">
         <v>1</v>
@@ -32589,19 +32651,19 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L590" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N590" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="591">
@@ -32612,21 +32674,21 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F591" t="b">
         <v>1</v>
@@ -32639,19 +32701,19 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L591" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N591" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="592">
@@ -32662,12 +32724,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -32697,7 +32759,7 @@
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N592" s="1" t="n">
@@ -32712,21 +32774,21 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F593" t="b">
         <v>1</v>
@@ -32739,15 +32801,15 @@
       <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L593" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N593" s="1" t="n">
@@ -32762,21 +32824,21 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F594" t="b">
         <v>1</v>
@@ -32789,15 +32851,15 @@
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L594" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N594" s="1" t="n">
@@ -32812,12 +32874,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -32839,13 +32901,17 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L595" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M595" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N595" s="1" t="n">
         <v>46050</v>
       </c>
@@ -32858,12 +32924,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -32904,21 +32970,21 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F597" t="b">
         <v>1</v>
@@ -32931,19 +32997,15 @@
       <c r="J597" t="inlineStr"/>
       <c r="K597" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L597" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M597" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M597" t="inlineStr"/>
       <c r="N597" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="598">
@@ -32954,21 +33016,21 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F598" t="b">
         <v>1</v>
@@ -32981,19 +33043,19 @@
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L598" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N598" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="599">
@@ -33004,12 +33066,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -33031,15 +33093,15 @@
       <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L599" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N599" s="1" t="n">
@@ -33054,12 +33116,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -33089,7 +33151,7 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N600" s="1" t="n">
@@ -33104,21 +33166,21 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F601" t="b">
         <v>1</v>
@@ -33131,15 +33193,15 @@
       <c r="J601" t="inlineStr"/>
       <c r="K601" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L601" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N601" s="1" t="n">
@@ -33154,21 +33216,21 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F602" t="b">
         <v>1</v>
@@ -33189,7 +33251,7 @@
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N602" s="1" t="n">
@@ -33204,21 +33266,21 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F603" t="b">
         <v>1</v>
@@ -33231,19 +33293,19 @@
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L603" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N603" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="604">
@@ -33254,21 +33316,21 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F604" t="b">
         <v>1</v>
@@ -33281,15 +33343,15 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L604" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N604" s="1" t="n">
@@ -33304,12 +33366,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -33339,7 +33401,7 @@
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N605" s="1" t="n">
@@ -33354,21 +33416,21 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F606" t="b">
         <v>1</v>
@@ -33381,19 +33443,19 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L606" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N606" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="607">
@@ -33404,21 +33466,21 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>2026-03-03 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46084.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F607" t="b">
         <v>1</v>
@@ -33431,15 +33493,15 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L607" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N607" s="1" t="n">
@@ -33454,21 +33516,21 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F608" t="b">
         <v>1</v>
@@ -33481,19 +33543,19 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L608" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N608" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="609">
@@ -33504,12 +33566,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -33539,7 +33601,7 @@
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N609" s="1" t="n">
@@ -33554,12 +33616,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -33589,7 +33651,7 @@
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N610" s="1" t="n">
@@ -33604,21 +33666,21 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>AI Champions: Frontier AI Phase 1</t>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>2026-03-12 10:34</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46093.44027777778</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F611" t="b">
         <v>1</v>
@@ -33631,15 +33693,15 @@
       <c r="J611" t="inlineStr"/>
       <c r="K611" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L611" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£15.0 million</t>
         </is>
       </c>
       <c r="N611" s="1" t="n">
@@ -33654,21 +33716,21 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Frontier AI Discovery</t>
+          <t>AI Champions: Frontier AI Phase 1</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-12 10:34</t>
         </is>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46093.44027777778</v>
       </c>
       <c r="F612" t="b">
         <v>1</v>
@@ -33681,15 +33743,15 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L612" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N612" s="1" t="n">
@@ -33704,12 +33766,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Secure Software for Resilient Growth</t>
+          <t>Frontier AI Discovery</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -33731,15 +33793,15 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L613" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N613" s="1" t="n">
@@ -33754,12 +33816,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+          <t>Secure Software for Resilient Growth</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -33781,15 +33843,15 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>Wednesday 22 April 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L614" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N614" s="1" t="n">
@@ -33804,21 +33866,21 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Frontier AI Benchmarking Datasets</t>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>2026-03-23 10:49</t>
+          <t>2026-03-17 10:45</t>
         </is>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46104.45069444444</v>
+        <v>46098.44791666666</v>
       </c>
       <c r="F615" t="b">
         <v>1</v>
@@ -33831,19 +33893,19 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 22 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L615" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N615" s="1" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="616">
@@ -33854,21 +33916,21 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing: Labs of the Future</t>
+          <t>Frontier AI Benchmarking Datasets</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>2026-03-24 10:47</t>
+          <t>2026-03-23 10:49</t>
         </is>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46105.44930555556</v>
+        <v>46104.45069444444</v>
       </c>
       <c r="F616" t="b">
         <v>1</v>
@@ -33889,7 +33951,7 @@
       </c>
       <c r="M616" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N616" s="1" t="n">
@@ -33904,12 +33966,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
+          <t>Medicines Manufacturing: Labs of the Future</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -33931,15 +33993,15 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L617" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N617" s="1" t="n">
@@ -33954,12 +34016,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -33989,7 +34051,7 @@
       </c>
       <c r="M618" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N618" s="1" t="n">
@@ -34004,21 +34066,21 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>2026-03-26 10:49</t>
+          <t>2026-03-24 10:47</t>
         </is>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46107.45069444444</v>
+        <v>46105.44930555556</v>
       </c>
       <c r="F619" t="b">
         <v>1</v>
@@ -34031,19 +34093,19 @@
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L619" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M619" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N619" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="620">
@@ -34054,12 +34116,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -34104,12 +34166,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -34154,21 +34216,21 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>2026-03-27 10:43</t>
+          <t>2026-03-26 10:49</t>
         </is>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46108.44652777778</v>
+        <v>46107.45069444444</v>
       </c>
       <c r="F622" t="b">
         <v>1</v>
@@ -34181,15 +34243,15 @@
       <c r="J622" t="inlineStr"/>
       <c r="K622" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L622" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M622" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N622" s="1" t="n">
@@ -34204,21 +34266,21 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
+          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>2026-03-28 10:27</t>
+          <t>2026-03-27 10:43</t>
         </is>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46109.43541666667</v>
+        <v>46108.44652777778</v>
       </c>
       <c r="F623" t="b">
         <v>1</v>
@@ -34231,15 +34293,15 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>Friday 29 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L623" s="1" t="n">
-        <v>46171.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M623" t="inlineStr">
         <is>
-          <t>£14.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N623" s="1" t="n">
@@ -34254,21 +34316,21 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: industrial research</t>
+          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>2026-04-01 10:50</t>
+          <t>2026-03-28 10:27</t>
         </is>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46113.45138888889</v>
+        <v>46109.43541666667</v>
       </c>
       <c r="F624" t="b">
         <v>1</v>
@@ -34281,19 +34343,19 @@
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Friday 29 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L624" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="M624" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£14.0 million</t>
         </is>
       </c>
       <c r="N624" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="625">
@@ -34304,12 +34366,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: feasibility studies</t>
+          <t>Future offshore wind technologies: industrial research</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -34339,7 +34401,7 @@
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N625" s="1" t="n">
@@ -34354,12 +34416,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Solution Development for Advanced Connectivity Technologies</t>
+          <t>Future offshore wind technologies: feasibility studies</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -34381,15 +34443,15 @@
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
-          <t>Wednesday 13 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L626" s="1" t="n">
-        <v>46155.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M626" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N626" s="1" t="n">
@@ -34404,12 +34466,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
+          <t>Solution Development for Advanced Connectivity Technologies</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -34431,15 +34493,15 @@
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 13 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L627" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="M627" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N627" s="1" t="n">
@@ -34454,21 +34516,21 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
+          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>2026-04-07 10:51</t>
+          <t>2026-04-01 10:50</t>
         </is>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46119.45208333333</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="F628" t="b">
         <v>1</v>
@@ -34481,15 +34543,15 @@
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>Wednesday 20 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L628" s="1" t="n">
-        <v>46162.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M628" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N628" s="1" t="n">
@@ -34504,21 +34566,21 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 7</t>
+          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>2026-04-09 10:54</t>
+          <t>2026-04-07 10:51</t>
         </is>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46121.45416666667</v>
+        <v>46119.45208333333</v>
       </c>
       <c r="F629" t="b">
         <v>1</v>
@@ -34531,19 +34593,19 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 20 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L629" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="M629" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N629" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="630">
@@ -34554,21 +34616,21 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Full ADOPT Grant: Round 7</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>2026-04-11 10:30</t>
+          <t>2026-04-09 10:54</t>
         </is>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46123.4375</v>
+        <v>46121.45416666667</v>
       </c>
       <c r="F630" t="b">
         <v>1</v>
@@ -34581,13 +34643,15 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Wednesday 1 July 2026 12:00pm</t>
-        </is>
-      </c>
-      <c r="L630" t="inlineStr"/>
+          <t>Wednesday 3 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L630" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
       <c r="M630" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N630" s="1" t="n">
@@ -34602,21 +34666,21 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Battery innovation feasibility studies round 2</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>2026-04-14 10:58</t>
+          <t>2026-04-11 10:30</t>
         </is>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46126.45694444444</v>
+        <v>46123.4375</v>
       </c>
       <c r="F631" t="b">
         <v>1</v>
@@ -34629,15 +34693,13 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L631" s="1" t="n">
-        <v>46169.45833333334</v>
-      </c>
+          <t>Wednesday 1 July 2026 12:00pm</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr"/>
       <c r="M631" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N631" s="1" t="n">
@@ -34652,12 +34714,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Battery innovation concept development round 2</t>
+          <t>Battery innovation feasibility studies round 2</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -34687,7 +34749,7 @@
       </c>
       <c r="M632" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N632" s="1" t="n">
@@ -34702,21 +34764,21 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 8</t>
+          <t>Battery innovation concept development round 2</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>2026-04-15 10:55</t>
+          <t>2026-04-14 10:58</t>
         </is>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46127.45486111111</v>
+        <v>46126.45694444444</v>
       </c>
       <c r="F633" t="b">
         <v>1</v>
@@ -34737,11 +34799,11 @@
       </c>
       <c r="M633" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N633" s="1" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="634">
@@ -34752,21 +34814,21 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
+          <t>ADOPT Facilitator Support Grant: Round 8</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>2026-04-18 10:35</t>
+          <t>2026-04-15 10:55</t>
         </is>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46130.44097222222</v>
+        <v>46127.45486111111</v>
       </c>
       <c r="F634" t="b">
         <v>1</v>
@@ -34779,15 +34841,15 @@
       <c r="J634" t="inlineStr"/>
       <c r="K634" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L634" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M634" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N634" s="1" t="n">
@@ -34802,21 +34864,21 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
+          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>2026-04-20 11:16</t>
+          <t>2026-04-18 10:35</t>
         </is>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46132.46944444445</v>
+        <v>46130.44097222222</v>
       </c>
       <c r="F635" t="b">
         <v>1</v>
@@ -34829,15 +34891,15 @@
       <c r="J635" t="inlineStr"/>
       <c r="K635" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L635" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M635" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N635" s="1" t="n">
@@ -34852,21 +34914,21 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation: CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>2026-04-21 11:02</t>
+          <t>2026-04-20 11:16</t>
         </is>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46133.45972222222</v>
+        <v>46132.46944444445</v>
       </c>
       <c r="F636" t="b">
         <v>1</v>
@@ -34879,15 +34941,15 @@
       <c r="J636" t="inlineStr"/>
       <c r="K636" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L636" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M636" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N636" s="1" t="n">
@@ -34902,21 +34964,21 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
+          <t>Advanced manufacturing supply chain innovation: CRD</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>2026-04-22 11:00</t>
+          <t>2026-04-21 11:02</t>
         </is>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46133.45972222222</v>
       </c>
       <c r="F637" t="b">
         <v>1</v>
@@ -34929,13 +34991,19 @@
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L637" t="inlineStr"/>
-      <c r="M637" t="inlineStr"/>
+          <t>Wednesday 10 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L637" s="1" t="n">
+        <v>46183.45833333334</v>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
       <c r="N637" s="1" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="638">
@@ -34946,21 +35014,21 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>2026-04-23 11:03</t>
+          <t>2026-04-22 11:00</t>
         </is>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46135.46041666667</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="F638" t="b">
         <v>1</v>
@@ -34973,17 +35041,11 @@
       <c r="J638" t="inlineStr"/>
       <c r="K638" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L638" s="1" t="n">
-        <v>46183.45833333334</v>
-      </c>
-      <c r="M638" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr"/>
       <c r="N638" s="1" t="n">
         <v>46134</v>
       </c>
@@ -34996,21 +35058,21 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Dual-use aviation systems and autonomy</t>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>2026-04-28 11:42</t>
+          <t>2026-04-23 11:03</t>
         </is>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46140.4875</v>
+        <v>46135.46041666667</v>
       </c>
       <c r="F639" t="b">
         <v>1</v>
@@ -35023,15 +35085,15 @@
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L639" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M639" t="inlineStr">
         <is>
-          <t>£1.2 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N639" s="1" t="n">
@@ -35046,12 +35108,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Counter UAS Technologies</t>
+          <t>Dual-use aviation systems and autonomy</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -35096,21 +35158,21 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility studies Rd 2</t>
+          <t>Counter UAS Technologies</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2469/overview/63ad7c49-77d4-4e13-b07f-0078c28d718e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>2026-04-30 11:25</t>
+          <t>2026-04-28 11:42</t>
         </is>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46142.47569444445</v>
+        <v>46140.4875</v>
       </c>
       <c r="F641" t="b">
         <v>1</v>
@@ -35123,19 +35185,19 @@
       <c r="J641" t="inlineStr"/>
       <c r="K641" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L641" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.2 million</t>
         </is>
       </c>
       <c r="N641" s="1" t="n">
-        <v>46141</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="642">
@@ -35146,21 +35208,21 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>CfI: Boosting fathers’ engagement to improve child outcomes</t>
+          <t>National Materials Innovation Programme: Feasibility studies Rd 2</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2458/overview/bd6562cf-e556-4860-9348-663db48bb1a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2469/overview/63ad7c49-77d4-4e13-b07f-0078c28d718e</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>2026-05-05 11:13</t>
+          <t>2026-04-30 11:25</t>
         </is>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46147.46736111111</v>
+        <v>46142.47569444445</v>
       </c>
       <c r="F642" t="b">
         <v>1</v>
@@ -35173,15 +35235,15 @@
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L642" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M642" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N642" s="1" t="n">
@@ -35196,21 +35258,21 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Battery Innovation Programme: Battery skills initiatives</t>
+          <t>CfI: Boosting fathers’ engagement to improve child outcomes</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2449/overview/34dd1264-cf19-4a9b-90bf-755e413085a5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2458/overview/bd6562cf-e556-4860-9348-663db48bb1a8</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>2026-05-07 11:43</t>
+          <t>2026-05-05 11:13</t>
         </is>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46149.48819444444</v>
+        <v>46147.46736111111</v>
       </c>
       <c r="F643" t="b">
         <v>1</v>
@@ -35223,19 +35285,19 @@
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr">
         <is>
-          <t>Thursday 18 June 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L643" s="1" t="n">
-        <v>46191.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M643" t="inlineStr">
         <is>
-          <t>£1.2 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N643" s="1" t="n">
-        <v>46148</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="644">
@@ -35246,21 +35308,21 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>Battery Innovation Programme: Battery skills initiatives</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2472/overview/8d51ea8e-212a-4a55-8e32-3237f92a86f2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2449/overview/34dd1264-cf19-4a9b-90bf-755e413085a5</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>2026-05-09 10:53</t>
+          <t>2026-05-07 11:43</t>
         </is>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46151.45347222222</v>
+        <v>46149.48819444444</v>
       </c>
       <c r="F644" t="b">
         <v>1</v>
@@ -35273,15 +35335,15 @@
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr">
         <is>
-          <t>Wednesday 17 June 2026 11:00am</t>
+          <t>Thursday 18 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L644" s="1" t="n">
-        <v>46190.45833333334</v>
+        <v>46191.45833333334</v>
       </c>
       <c r="M644" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£1.2 million</t>
         </is>
       </c>
       <c r="N644" s="1" t="n">
@@ -35296,12 +35358,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Solution Development for Advanced Connectivity Technologies: applications with academic partners</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2474/overview/7dec743d-f024-43d9-8bfc-62331c987d09</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2472/overview/8d51ea8e-212a-4a55-8e32-3237f92a86f2</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -35323,15 +35385,15 @@
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr">
         <is>
-          <t>Wednesday 13 May 2026 11:00am</t>
+          <t>Wednesday 17 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L645" s="1" t="n">
-        <v>46155.45833333334</v>
+        <v>46190.45833333334</v>
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N645" s="1" t="n">
@@ -35346,21 +35408,21 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: FOAK26</t>
+          <t>Solution Development for Advanced Connectivity Technologies: applications with academic partners</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2475/overview/6fba05b0-d73b-4a33-886e-cb0950f1252a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2474/overview/7dec743d-f024-43d9-8bfc-62331c987d09</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>2026-05-12 11:50</t>
+          <t>2026-05-09 10:53</t>
         </is>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46154.49305555555</v>
+        <v>46151.45347222222</v>
       </c>
       <c r="F646" t="b">
         <v>1</v>
@@ -35373,15 +35435,15 @@
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 13 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L646" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t>£210,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N646" s="1" t="n">
@@ -35396,21 +35458,21 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer Partnerships 6 (AKT 6)</t>
+          <t>Contracts for Innovation: FOAK26</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2473/overview/d9a164dd-2094-4590-baa7-a057279d80a3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2475/overview/6fba05b0-d73b-4a33-886e-cb0950f1252a</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>2026-05-16 10:59</t>
+          <t>2026-05-12 11:50</t>
         </is>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46158.45763888889</v>
+        <v>46154.49305555555</v>
       </c>
       <c r="F647" t="b">
         <v>1</v>
@@ -35423,19 +35485,19 @@
       <c r="J647" t="inlineStr"/>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L647" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£210,000</t>
         </is>
       </c>
       <c r="N647" s="1" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="648">
@@ -35446,21 +35508,21 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>Accelerated Knowledge Transfer Partnerships 6 (AKT 6)</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2478/overview/77f0cc95-dd1b-450f-a02d-e83046b464c1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2473/overview/d9a164dd-2094-4590-baa7-a057279d80a3</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>2026-05-18 13:41</t>
+          <t>2026-05-16 10:59</t>
         </is>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46160.57013888889</v>
+        <v>46158.45763888889</v>
       </c>
       <c r="F648" t="b">
         <v>1</v>
@@ -35473,15 +35535,15 @@
       <c r="J648" t="inlineStr"/>
       <c r="K648" t="inlineStr">
         <is>
-          <t>Tuesday 1 September 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L648" s="1" t="n">
-        <v>46266.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N648" s="1" t="n">
@@ -35496,21 +35558,21 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>CfI Improving Outcomes for Children Experiencing Homelessness</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2460/overview/d840aec6-c35d-4d86-a524-2b4c5a9bf9b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2478/overview/77f0cc95-dd1b-450f-a02d-e83046b464c1</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>2026-05-19 12:36</t>
+          <t>2026-05-18 13:41</t>
         </is>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46161.525</v>
+        <v>46160.57013888889</v>
       </c>
       <c r="F649" t="b">
         <v>1</v>
@@ -35523,15 +35585,15 @@
       <c r="J649" t="inlineStr"/>
       <c r="K649" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Tuesday 1 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L649" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46266.45833333334</v>
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N649" s="1" t="n">
@@ -35546,21 +35608,21 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: industrial research (Research Organisations)</t>
+          <t>CfI Improving Outcomes for Children Experiencing Homelessness</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2497/overview/1abf98e8-4873-4fb7-b9d0-e702a2c9d80a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2460/overview/d840aec6-c35d-4d86-a524-2b4c5a9bf9b3</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>2026-05-28 13:43</t>
+          <t>2026-05-19 12:36</t>
         </is>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46170.57152777778</v>
+        <v>46161.525</v>
       </c>
       <c r="F650" t="b">
         <v>1</v>
@@ -35573,19 +35635,19 @@
       <c r="J650" t="inlineStr"/>
       <c r="K650" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L650" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N650" s="1" t="n">
-        <v>46169</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="651">
@@ -35596,12 +35658,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C6</t>
+          <t>Future offshore wind technologies: industrial research (Research Organisations)</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2480/overview/96372f42-c714-4d17-91b0-dd75b9a80e17</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2497/overview/1abf98e8-4873-4fb7-b9d0-e702a2c9d80a</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -35623,15 +35685,15 @@
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L651" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M651" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N651" s="1" t="n">
@@ -35646,12 +35708,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Discovery C6</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C6</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2484/overview/770c0946-2e24-4566-bab1-2bf1c1dd2b38</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2480/overview/96372f42-c714-4d17-91b0-dd75b9a80e17</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -35696,21 +35758,21 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 7 - Academic Partners</t>
+          <t>Ofgem Strategic Innovation Fund Discovery C6</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2500/overview/d7508935-cc7f-4971-8f0f-074f80317ed4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2484/overview/770c0946-2e24-4566-bab1-2bf1c1dd2b38</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>2026-05-29 12:45</t>
+          <t>2026-05-28 13:43</t>
         </is>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46171.53125</v>
+        <v>46170.57152777778</v>
       </c>
       <c r="F653" t="b">
         <v>1</v>
@@ -35723,15 +35785,15 @@
       <c r="J653" t="inlineStr"/>
       <c r="K653" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L653" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M653" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N653" s="1" t="n">
@@ -35746,12 +35808,12 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 9</t>
+          <t>Full ADOPT Grant: Round 7 - Academic Partners</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2482/overview/a17ac084-56fa-4679-8d35-1f5602f27d29</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2500/overview/d7508935-cc7f-4971-8f0f-074f80317ed4</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -35773,15 +35835,15 @@
       <c r="J654" t="inlineStr"/>
       <c r="K654" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L654" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M654" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N654" s="1" t="n">
@@ -35796,21 +35858,21 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
+          <t>ADOPT Facilitator Support Grant: Round 9</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2482/overview/a17ac084-56fa-4679-8d35-1f5602f27d29</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>2026-06-03 14:24</t>
+          <t>2026-05-29 12:45</t>
         </is>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46176.6</v>
+        <v>46171.53125</v>
       </c>
       <c r="F655" t="b">
         <v>1</v>
@@ -35823,19 +35885,19 @@
       <c r="J655" t="inlineStr"/>
       <c r="K655" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L655" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M655" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N655" s="1" t="n">
-        <v>46176</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="656">
@@ -35846,12 +35908,12 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>ACTASAP Pilot Phase 1</t>
+          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2502/overview/35ca10fb-d4f5-4510-9ddd-e7e3133d2b6d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -35873,15 +35935,15 @@
       <c r="J656" t="inlineStr"/>
       <c r="K656" t="inlineStr">
         <is>
-          <t>Tuesday 28 July 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L656" s="1" t="n">
-        <v>46231.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M656" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N656" s="1" t="n">
@@ -35896,12 +35958,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Scaling Supply Chains for Quantum Enabled Sensing and PNT</t>
+          <t>ACTASAP Pilot Phase 1</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2495/overview/b2a4cd81-a226-4a11-83c8-966284542f59</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2502/overview/35ca10fb-d4f5-4510-9ddd-e7e3133d2b6d</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -35923,15 +35985,15 @@
       <c r="J657" t="inlineStr"/>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Tuesday 28 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L657" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46231.45833333334</v>
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N657" s="1" t="n">
@@ -35946,21 +36008,21 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 8</t>
+          <t>Scaling Supply Chains for Quantum Enabled Sensing and PNT</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2491/overview/77ba6cb6-c14d-41f7-84de-e45446636e50</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2495/overview/b2a4cd81-a226-4a11-83c8-966284542f59</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>2026-06-04 12:41</t>
+          <t>2026-06-03 14:24</t>
         </is>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46177.52847222222</v>
+        <v>46176.6</v>
       </c>
       <c r="F658" t="b">
         <v>1</v>
@@ -35973,15 +36035,15 @@
       <c r="J658" t="inlineStr"/>
       <c r="K658" t="inlineStr">
         <is>
-          <t>Wednesday 29 July 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L658" s="1" t="n">
-        <v>46232.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N658" s="1" t="n">
@@ -35996,21 +36058,21 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Innovation Loans Expression of Interest</t>
+          <t>Full ADOPT Grant: Round 8</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2491/overview/77ba6cb6-c14d-41f7-84de-e45446636e50</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>2026-06-05 12:33</t>
+          <t>2026-06-04 12:41</t>
         </is>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46178.52291666667</v>
+        <v>46177.52847222222</v>
       </c>
       <c r="F659" t="b">
         <v>1</v>
@@ -36023,13 +36085,15 @@
       <c r="J659" t="inlineStr"/>
       <c r="K659" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L659" t="inlineStr"/>
+          <t>Wednesday 29 July 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L659" s="1" t="n">
+        <v>46232.45833333334</v>
+      </c>
       <c r="M659" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N659" s="1" t="n">
@@ -36044,21 +36108,21 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body summer 2026</t>
+          <t>Innovation Loans Expression of Interest</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2504/overview/05f2babb-c5b0-4b37-80dc-3883b41bc2c7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2026-06-11 13:55</t>
+          <t>2026-06-05 12:33</t>
         </is>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46184.57986111111</v>
+        <v>46178.52291666667</v>
       </c>
       <c r="F660" t="b">
         <v>1</v>
@@ -36071,19 +36135,17 @@
       <c r="J660" t="inlineStr"/>
       <c r="K660" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L660" s="1" t="n">
-        <v>46211.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr"/>
       <c r="M660" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N660" s="1" t="n">
-        <v>46183</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="661">
@@ -36094,12 +36156,12 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Consumer Led Flexibility for the Clean Energy Superpower Mission</t>
+          <t>Robotics Adoption Central Convening Body summer 2026</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2509/overview/c1794f5a-06bf-41bb-8a13-3e657dacef54</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2504/overview/05f2babb-c5b0-4b37-80dc-3883b41bc2c7</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -36121,15 +36183,15 @@
       <c r="J661" t="inlineStr"/>
       <c r="K661" t="inlineStr">
         <is>
-          <t>Wednesday 26 August 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L661" s="1" t="n">
-        <v>46260.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M661" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N661" s="1" t="n">
@@ -36144,21 +36206,21 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>UK-Switzerland CR&amp;D Round 3</t>
+          <t>Consumer Led Flexibility for the Clean Energy Superpower Mission</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2512/overview/2f0a03c4-44b7-42dc-8845-70751b6bc531</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2509/overview/c1794f5a-06bf-41bb-8a13-3e657dacef54</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>2026-06-19 13:32</t>
+          <t>2026-06-11 13:55</t>
         </is>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46192.56388888889</v>
+        <v>46184.57986111111</v>
       </c>
       <c r="F662" t="b">
         <v>1</v>
@@ -36171,19 +36233,19 @@
       <c r="J662" t="inlineStr"/>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Thursday 3 September 2026 11:00am</t>
+          <t>Wednesday 26 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L662" s="1" t="n">
-        <v>46268.45833333334</v>
+        <v>46260.45833333334</v>
       </c>
       <c r="M662" t="inlineStr">
         <is>
-          <t>£450,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N662" s="1" t="n">
-        <v>46190</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="663">
@@ -36194,21 +36256,21 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>CfI: Earlier identification of UK children with SEN</t>
+          <t>UK-Switzerland CR&amp;D Round 3</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2511/overview/cc9f4bb9-55a5-4b4c-9843-015c385e021f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2512/overview/2f0a03c4-44b7-42dc-8845-70751b6bc531</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2026-06-22 15:20</t>
+          <t>2026-06-19 13:32</t>
         </is>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46195.63888888889</v>
+        <v>46192.56388888889</v>
       </c>
       <c r="F663" t="b">
         <v>1</v>
@@ -36221,15 +36283,15 @@
       <c r="J663" t="inlineStr"/>
       <c r="K663" t="inlineStr">
         <is>
-          <t>Wednesday 5 August 2026 11:00am</t>
+          <t>Thursday 3 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L663" s="1" t="n">
-        <v>46239.45833333334</v>
+        <v>46268.45833333334</v>
       </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>£500</t>
+          <t>£450,000</t>
         </is>
       </c>
       <c r="N663" s="1" t="n">
@@ -36244,12 +36306,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>DRIVE35: Scale Up Fund</t>
+          <t>CfI: Earlier identification of UK children with SEN</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2445/overview/a850ba04-f0b3-42c5-8dfa-03375731a884</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2511/overview/cc9f4bb9-55a5-4b4c-9843-015c385e021f</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -36271,13 +36333,15 @@
       <c r="J664" t="inlineStr"/>
       <c r="K664" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L664" t="inlineStr"/>
+          <t>Wednesday 5 August 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L664" s="1" t="n">
+        <v>46239.45833333334</v>
+      </c>
       <c r="M664" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£500</t>
         </is>
       </c>
       <c r="N664" s="1" t="n">
@@ -36292,21 +36356,21 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Next Wave: Breakthrough Wave 1</t>
+          <t>DRIVE35: Scale Up Fund</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2517/overview/6ff2066d-4639-44e6-bb4f-ce7099222739</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2445/overview/a850ba04-f0b3-42c5-8dfa-03375731a884</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>2026-06-23 12:29</t>
+          <t>2026-06-22 15:20</t>
         </is>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46196.52013888889</v>
+        <v>46195.63888888889</v>
       </c>
       <c r="F665" t="b">
         <v>1</v>
@@ -36319,15 +36383,13 @@
       <c r="J665" t="inlineStr"/>
       <c r="K665" t="inlineStr">
         <is>
-          <t>Tuesday 11 August 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L665" s="1" t="n">
-        <v>46245.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr"/>
       <c r="M665" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N665" s="1" t="n">
@@ -36342,21 +36404,21 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
+          <t>Next Wave: Breakthrough Wave 1</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2517/overview/6ff2066d-4639-44e6-bb4f-ce7099222739</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>2026-06-26 12:08</t>
+          <t>2026-06-23 12:29</t>
         </is>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46199.50555555556</v>
+        <v>46196.52013888889</v>
       </c>
       <c r="F666" t="b">
         <v>1</v>
@@ -36369,19 +36431,19 @@
       <c r="J666" t="inlineStr"/>
       <c r="K666" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Tuesday 11 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L666" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46245.45833333334</v>
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N666" s="1" t="n">
-        <v>46197</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="667">
@@ -36392,21 +36454,21 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>2026-06-27 11:24</t>
+          <t>2026-06-26 12:08</t>
         </is>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46200.475</v>
+        <v>46199.50555555556</v>
       </c>
       <c r="F667" t="b">
         <v>1</v>
@@ -36419,15 +36481,15 @@
       <c r="J667" t="inlineStr"/>
       <c r="K667" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L667" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M667" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N667" s="1" t="n">
@@ -36442,21 +36504,21 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 10</t>
+          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2520/overview/7b03dc59-645f-426d-a08f-6c6e6b6d6e0e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>2026-07-10 12:22</t>
+          <t>2026-06-27 11:24</t>
         </is>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46213.51527777778</v>
+        <v>46200.475</v>
       </c>
       <c r="F668" t="b">
         <v>1</v>
@@ -36469,19 +36531,19 @@
       <c r="J668" t="inlineStr"/>
       <c r="K668" t="inlineStr">
         <is>
-          <t>Wednesday 12 August 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L668" s="1" t="n">
-        <v>46246.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N668" s="1" t="n">
-        <v>46211</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="669">
@@ -36492,21 +36554,21 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 5</t>
+          <t>ADOPT Facilitator Support Grant: Round 10</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2529/overview/7a278b3b-4e22-4702-a8aa-7491d9a11e36</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2520/overview/7b03dc59-645f-426d-a08f-6c6e6b6d6e0e</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>2026-07-15 11:25</t>
+          <t>2026-07-10 12:22</t>
         </is>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46218.47569444445</v>
+        <v>46213.51527777778</v>
       </c>
       <c r="F669" t="b">
         <v>1</v>
@@ -36519,19 +36581,19 @@
       <c r="J669" t="inlineStr"/>
       <c r="K669" t="inlineStr">
         <is>
-          <t>Wednesday 9 September 2026 11:00am</t>
+          <t>Wednesday 12 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L669" s="1" t="n">
-        <v>46274.45833333334</v>
+        <v>46246.45833333334</v>
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N669" s="1" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="670">
@@ -36542,21 +36604,21 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Advanced Connectivity Technologies: New Innovators</t>
+          <t>Farming Innovation Programme: Feasibility Round 5</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2513/overview/cbe58d4f-05a7-4eca-976b-e2de751b47ae</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2529/overview/7a278b3b-4e22-4702-a8aa-7491d9a11e36</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>2026-07-17 11:18</t>
+          <t>2026-07-15 11:25</t>
         </is>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46220.47083333333</v>
+        <v>46218.47569444445</v>
       </c>
       <c r="F670" t="b">
         <v>1</v>
@@ -36569,15 +36631,15 @@
       <c r="J670" t="inlineStr"/>
       <c r="K670" t="inlineStr">
         <is>
-          <t>Wednesday 5 August 2026 11:00am</t>
+          <t>Wednesday 9 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L670" s="1" t="n">
-        <v>46239.45833333334</v>
+        <v>46274.45833333334</v>
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N670" s="1" t="n">
@@ -36592,21 +36654,21 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Ultra Long Duration Energy Storage Project Development Studies</t>
+          <t>Advanced Connectivity Technologies: New Innovators</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2531/overview/5f2a43fb-9581-4892-8e15-86c2c0c814cd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2513/overview/cbe58d4f-05a7-4eca-976b-e2de751b47ae</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>2026-08-03 12:52</t>
+          <t>2026-07-17 11:18</t>
         </is>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46237.53611111111</v>
+        <v>46220.47083333333</v>
       </c>
       <c r="F671" t="b">
         <v>1</v>
@@ -36619,19 +36681,19 @@
       <c r="J671" t="inlineStr"/>
       <c r="K671" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 5 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L671" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46239.45833333334</v>
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>£700,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N671" s="1" t="n">
-        <v>46232</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="672">
@@ -36642,12 +36704,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
+          <t>Ultra Long Duration Energy Storage Project Development Studies</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2531/overview/5f2a43fb-9581-4892-8e15-86c2c0c814cd</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -36677,7 +36739,7 @@
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£700,000</t>
         </is>
       </c>
       <c r="N672" s="1" t="n">
@@ -36692,21 +36754,21 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
+          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-03 12:52</t>
         </is>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46238.49930555555</v>
+        <v>46237.53611111111</v>
       </c>
       <c r="F673" t="b">
         <v>1</v>
@@ -36719,15 +36781,15 @@
       <c r="J673" t="inlineStr"/>
       <c r="K673" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L673" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N673" s="1" t="n">
@@ -36742,12 +36804,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
+          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -36777,7 +36839,7 @@
       </c>
       <c r="M674" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N674" s="1" t="n">
@@ -36792,21 +36854,21 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
+          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>2026-08-10 11:02</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46244.45972222222</v>
+        <v>46238.49930555555</v>
       </c>
       <c r="F675" t="b">
         <v>1</v>
@@ -36819,19 +36881,19 @@
       <c r="J675" t="inlineStr"/>
       <c r="K675" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L675" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N675" s="1" t="n">
-        <v>46239</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="676">
@@ -36842,21 +36904,21 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>UK-Singapore CRD 2026</t>
+          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>2026-08-13 10:57</t>
+          <t>2026-08-10 11:02</t>
         </is>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46247.45625</v>
+        <v>46244.45972222222</v>
       </c>
       <c r="F676" t="b">
         <v>1</v>
@@ -36869,19 +36931,19 @@
       <c r="J676" t="inlineStr"/>
       <c r="K676" t="inlineStr">
         <is>
-          <t>Wednesday 16 December 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L676" s="1" t="n">
-        <v>46372.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>£900,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N676" s="1" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="677">
@@ -36892,21 +36954,21 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 9</t>
+          <t>UK-Singapore CRD 2026</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>2026-08-14 10:53</t>
+          <t>2026-08-13 10:57</t>
         </is>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46248.45347222222</v>
+        <v>46247.45625</v>
       </c>
       <c r="F677" t="b">
         <v>1</v>
@@ -36919,15 +36981,15 @@
       <c r="J677" t="inlineStr"/>
       <c r="K677" t="inlineStr">
         <is>
-          <t>Wednesday 23 September 2026 11:00am</t>
+          <t>Wednesday 16 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L677" s="1" t="n">
-        <v>46288.45833333334</v>
+        <v>46372.45833333334</v>
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£900,000</t>
         </is>
       </c>
       <c r="N677" s="1" t="n">
@@ -36942,12 +37004,12 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
+          <t>Full ADOPT Grant: Round 9</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -36969,13 +37031,17 @@
       <c r="J678" t="inlineStr"/>
       <c r="K678" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 23 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L678" s="1" t="n">
-        <v>46309.45833333334</v>
-      </c>
-      <c r="M678" t="inlineStr"/>
+        <v>46288.45833333334</v>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>£200,000</t>
+        </is>
+      </c>
       <c r="N678" s="1" t="n">
         <v>46246</v>
       </c>
@@ -36988,21 +37054,21 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Advancing innovation in accelerated cancer diagnosis</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>2026-08-19 10:22</t>
+          <t>2026-08-14 10:53</t>
         </is>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46253.43194444444</v>
+        <v>46248.45347222222</v>
       </c>
       <c r="F679" t="b">
         <v>1</v>
@@ -37015,19 +37081,15 @@
       <c r="J679" t="inlineStr"/>
       <c r="K679" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L679" s="1" t="n">
-        <v>46323.45833333334</v>
-      </c>
-      <c r="M679" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>46309.45833333334</v>
+      </c>
+      <c r="M679" t="inlineStr"/>
       <c r="N679" s="1" t="n">
-        <v>46253</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="680">
@@ -37038,21 +37100,21 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 11</t>
+          <t>Advancing innovation in accelerated cancer diagnosis</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>2026-08-20 10:23</t>
+          <t>2026-08-19 10:22</t>
         </is>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46254.43263888889</v>
+        <v>46253.43194444444</v>
       </c>
       <c r="F680" t="b">
         <v>1</v>
@@ -37065,15 +37127,15 @@
       <c r="J680" t="inlineStr"/>
       <c r="K680" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L680" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M680" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N680" s="1" t="n">
@@ -37088,21 +37150,21 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
+          <t>ADOPT Facilitator Support Grant: Round 11</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17</t>
+          <t>2026-08-20 10:23</t>
         </is>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46256.42847222222</v>
+        <v>46254.43263888889</v>
       </c>
       <c r="F681" t="b">
         <v>1</v>
@@ -37115,15 +37177,15 @@
       <c r="J681" t="inlineStr"/>
       <c r="K681" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L681" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M681" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N681" s="1" t="n">
@@ -37138,21 +37200,21 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
+          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>2026-08-26 10:29</t>
+          <t>2026-08-22 10:17</t>
         </is>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46260.43680555555</v>
+        <v>46256.42847222222</v>
       </c>
       <c r="F682" t="b">
         <v>1</v>
@@ -37165,19 +37227,19 @@
       <c r="J682" t="inlineStr"/>
       <c r="K682" t="inlineStr">
         <is>
-          <t>Wednesday 7 October 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L682" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M682" t="inlineStr">
         <is>
-          <t>£80,420</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N682" s="1" t="n">
-        <v>46260</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="683">
@@ -37188,21 +37250,21 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
+          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2026-08-28 21:03</t>
+          <t>2026-08-26 10:29</t>
         </is>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46262.87708333333</v>
+        <v>46260.43680555555</v>
       </c>
       <c r="F683" t="b">
         <v>1</v>
@@ -37215,15 +37277,15 @@
       <c r="J683" t="inlineStr"/>
       <c r="K683" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 7 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L683" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£80,420</t>
         </is>
       </c>
       <c r="N683" s="1" t="n">
@@ -37238,12 +37300,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Investor Partnerships – ACT and Semiconductors</t>
+          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -37265,15 +37327,15 @@
       <c r="J684" t="inlineStr"/>
       <c r="K684" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L684" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N684" s="1" t="n">
@@ -37288,21 +37350,21 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
+          <t>Investor Partnerships – ACT and Semiconductors</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>2026-09-01 14:28</t>
+          <t>2026-08-28 21:03</t>
         </is>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46266.60277777778</v>
+        <v>46262.87708333333</v>
       </c>
       <c r="F685" t="b">
         <v>1</v>
@@ -37323,7 +37385,7 @@
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N685" s="1" t="n">
@@ -37338,12 +37400,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -37373,7 +37435,7 @@
       </c>
       <c r="M686" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N686" s="1" t="n">
@@ -37388,21 +37450,21 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing Data Institute: Phase 1</t>
+          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-01 14:28</t>
         </is>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46269.58055555556</v>
+        <v>46266.60277777778</v>
       </c>
       <c r="F687" t="b">
         <v>1</v>
@@ -37423,11 +37485,11 @@
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N687" s="1" t="n">
-        <v>46267</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="688">
@@ -37438,21 +37500,21 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
+          <t>Medicines Manufacturing Data Institute: Phase 1</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46272.64375</v>
+        <v>46269.58055555556</v>
       </c>
       <c r="F688" t="b">
         <v>1</v>
@@ -37465,15 +37527,15 @@
       <c r="J688" t="inlineStr"/>
       <c r="K688" t="inlineStr">
         <is>
-          <t>Tuesday 3 November 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L688" s="1" t="n">
-        <v>46329.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M688" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N688" s="1" t="n">
@@ -37488,12 +37550,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Engineering Biology Access to Infrastructure Pilot</t>
+          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -37515,15 +37577,15 @@
       <c r="J689" t="inlineStr"/>
       <c r="K689" t="inlineStr">
         <is>
-          <t>Wednesday 21 October 2026 11:00am</t>
+          <t>Tuesday 3 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L689" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46329.45833333334</v>
       </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N689" s="1" t="n">
@@ -37538,21 +37600,21 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
+          <t>Engineering Biology Access to Infrastructure Pilot</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-07 15:27</t>
         </is>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46276.58333333334</v>
+        <v>46272.64375</v>
       </c>
       <c r="F690" t="b">
         <v>1</v>
@@ -37565,19 +37627,19 @@
       <c r="J690" t="inlineStr"/>
       <c r="K690" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 21 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L690" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>£700,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N690" s="1" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="691">
@@ -37588,12 +37650,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Battery Innovation: Feasibility Studies Rd 3</t>
+          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -37615,15 +37677,15 @@
       <c r="J691" t="inlineStr"/>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L691" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£700,000</t>
         </is>
       </c>
       <c r="N691" s="1" t="n">
@@ -37638,12 +37700,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Battery Innovation: Concept Development Rd 3</t>
+          <t>Battery Innovation: Feasibility Studies Rd 3</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -37673,7 +37735,7 @@
       </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N692" s="1" t="n">
@@ -37688,21 +37750,21 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>CfI: Innovation in play to improve child outcomes</t>
+          <t>Battery Innovation: Concept Development Rd 3</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2573/overview/0260e1f5-c985-4858-aee3-57a9e56f19fe</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46280.60763888889</v>
+        <v>46276.58333333334</v>
       </c>
       <c r="F693" t="b">
         <v>1</v>
@@ -37715,15 +37777,15 @@
       <c r="J693" t="inlineStr"/>
       <c r="K693" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L693" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N693" s="1" t="n">
@@ -37748,11 +37810,11 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36</t>
+          <t>2026-09-15 14:35</t>
         </is>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46282.60833333333</v>
+        <v>46280.60763888889</v>
       </c>
       <c r="F694" t="b">
         <v>1</v>
@@ -37777,7 +37839,7 @@
         </is>
       </c>
       <c r="N694" s="1" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="695">
@@ -37788,12 +37850,12 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
+          <t>CfI: Innovation in play to improve child outcomes</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2573/overview/0260e1f5-c985-4858-aee3-57a9e56f19fe</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -37815,15 +37877,15 @@
       <c r="J695" t="inlineStr"/>
       <c r="K695" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L695" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M695" t="inlineStr">
         <is>
-          <t>£700,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N695" s="1" t="n">
@@ -37838,12 +37900,12 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Battery Innovation: Feasibility Studies Rd 3</t>
+          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -37865,15 +37927,15 @@
       <c r="J696" t="inlineStr"/>
       <c r="K696" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L696" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£700,000</t>
         </is>
       </c>
       <c r="N696" s="1" t="n">
@@ -37888,12 +37950,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Battery Innovation: Concept Development Rd 3</t>
+          <t>Battery Innovation: Feasibility Studies Rd 3</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -37923,7 +37985,7 @@
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N697" s="1" t="n">
@@ -37938,12 +38000,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
+          <t>Battery Innovation: Concept Development Rd 3</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -37965,15 +38027,15 @@
       <c r="J698" t="inlineStr"/>
       <c r="K698" t="inlineStr">
         <is>
-          <t>Tuesday 3 November 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L698" s="1" t="n">
-        <v>46329.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M698" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N698" s="1" t="n">
@@ -37988,12 +38050,12 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing Data Institute: Phase 1</t>
+          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -38015,15 +38077,15 @@
       <c r="J699" t="inlineStr"/>
       <c r="K699" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Tuesday 3 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L699" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46329.45833333334</v>
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N699" s="1" t="n">
@@ -38038,12 +38100,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Engineering Biology Access to Infrastructure Pilot</t>
+          <t>Medicines Manufacturing Data Institute: Phase 1</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -38065,15 +38127,15 @@
       <c r="J700" t="inlineStr"/>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Wednesday 21 October 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L700" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N700" s="1" t="n">
@@ -38088,12 +38150,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
+          <t>Engineering Biology Access to Infrastructure Pilot</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -38115,15 +38177,15 @@
       <c r="J701" t="inlineStr"/>
       <c r="K701" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 21 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L701" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N701" s="1" t="n">
@@ -38138,12 +38200,12 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Investor Partnerships – ACT and Semiconductors</t>
+          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -38165,15 +38227,15 @@
       <c r="J702" t="inlineStr"/>
       <c r="K702" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L702" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N702" s="1" t="n">
@@ -38188,12 +38250,12 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
+          <t>Investor Partnerships – ACT and Semiconductors</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -38223,7 +38285,7 @@
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N703" s="1" t="n">
@@ -38238,12 +38300,12 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -38273,7 +38335,7 @@
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N704" s="1" t="n">
@@ -38288,12 +38350,12 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Advancing innovation in accelerated cancer diagnosis</t>
+          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -38315,15 +38377,15 @@
       <c r="J705" t="inlineStr"/>
       <c r="K705" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L705" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N705" s="1" t="n">
@@ -38338,12 +38400,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
+          <t>Advancing innovation in accelerated cancer diagnosis</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -38365,15 +38427,15 @@
       <c r="J706" t="inlineStr"/>
       <c r="K706" t="inlineStr">
         <is>
-          <t>Wednesday 7 October 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L706" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>£80,420</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N706" s="1" t="n">
@@ -38388,12 +38450,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>UK-Singapore CRD 2026</t>
+          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -38415,15 +38477,15 @@
       <c r="J707" t="inlineStr"/>
       <c r="K707" t="inlineStr">
         <is>
-          <t>Wednesday 16 December 2026 11:00am</t>
+          <t>Wednesday 7 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L707" s="1" t="n">
-        <v>46372.45833333334</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>£900,000</t>
+          <t>£80,420</t>
         </is>
       </c>
       <c r="N707" s="1" t="n">
@@ -38438,12 +38500,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
+          <t>UK-Singapore CRD 2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -38465,15 +38527,15 @@
       <c r="J708" t="inlineStr"/>
       <c r="K708" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Wednesday 16 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46372.45833333334</v>
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£900,000</t>
         </is>
       </c>
       <c r="N708" s="1" t="n">
@@ -38488,12 +38550,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 11</t>
+          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -38515,15 +38577,15 @@
       <c r="J709" t="inlineStr"/>
       <c r="K709" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N709" s="1" t="n">
@@ -38538,12 +38600,12 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 9</t>
+          <t>ADOPT Facilitator Support Grant: Round 11</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -38565,15 +38627,15 @@
       <c r="J710" t="inlineStr"/>
       <c r="K710" t="inlineStr">
         <is>
-          <t>Wednesday 7 October 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N710" s="1" t="n">
@@ -38588,12 +38650,12 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
+          <t>Full ADOPT Grant: Round 9</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -38615,13 +38677,17 @@
       <c r="J711" t="inlineStr"/>
       <c r="K711" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 7 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46309.45833333334</v>
-      </c>
-      <c r="M711" t="inlineStr"/>
+        <v>46302.45833333334</v>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>£200,000</t>
+        </is>
+      </c>
       <c r="N711" s="1" t="n">
         <v>46281</v>
       </c>
@@ -38634,12 +38700,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -38661,17 +38727,13 @@
       <c r="J712" t="inlineStr"/>
       <c r="K712" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46330.45833333334</v>
-      </c>
-      <c r="M712" t="inlineStr">
-        <is>
-          <t>£20.0 million</t>
-        </is>
-      </c>
+        <v>46309.45833333334</v>
+      </c>
+      <c r="M712" t="inlineStr"/>
       <c r="N712" s="1" t="n">
         <v>46281</v>
       </c>
@@ -38684,12 +38746,12 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
+          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -38711,15 +38773,15 @@
       <c r="J713" t="inlineStr"/>
       <c r="K713" t="inlineStr">
         <is>
-          <t>Thursday 24 September 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46289.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N713" s="1" t="n">
@@ -38734,12 +38796,12 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
+          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -38761,15 +38823,15 @@
       <c r="J714" t="inlineStr"/>
       <c r="K714" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Thursday 24 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46289.45833333334</v>
       </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N714" s="1" t="n">
@@ -38784,12 +38846,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
+          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -38811,15 +38873,15 @@
       <c r="J715" t="inlineStr"/>
       <c r="K715" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L715" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N715" s="1" t="n">
@@ -38834,12 +38896,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
+          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -38861,15 +38923,15 @@
       <c r="J716" t="inlineStr"/>
       <c r="K716" t="inlineStr">
         <is>
-          <t>Friday 2 October 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L716" s="1" t="n">
-        <v>46297.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N716" s="1" t="n">
@@ -38884,12 +38946,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
+          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -38911,15 +38973,15 @@
       <c r="J717" t="inlineStr"/>
       <c r="K717" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Friday 2 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L717" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="M717" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N717" s="1" t="n">
@@ -38934,12 +38996,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -38961,15 +39023,15 @@
       <c r="J718" t="inlineStr"/>
       <c r="K718" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L718" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N718" s="1" t="n">
@@ -38984,12 +39046,12 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Innovation Loans Expression of Interest</t>
+          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -39011,13 +39073,15 @@
       <c r="J719" t="inlineStr"/>
       <c r="K719" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr"/>
+          <t>Wednesday 4 November 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L719" s="1" t="n">
+        <v>46330.45833333334</v>
+      </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N719" s="1" t="n">
@@ -39032,12 +39096,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
+          <t>Innovation Loans Expression of Interest</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -39059,15 +39123,13 @@
       <c r="J720" t="inlineStr"/>
       <c r="K720" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L720" s="1" t="n">
-        <v>46283.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr"/>
       <c r="M720" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N720" s="1" t="n">
@@ -39082,12 +39144,12 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -39132,12 +39194,12 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -39182,21 +39244,21 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C7</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2550/overview/5cbb2d13-74bb-41b1-be19-005376930f80</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>2026-09-18 14:02</t>
+          <t>2026-09-17 14:36</t>
         </is>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46283.58472222222</v>
+        <v>46282.60833333333</v>
       </c>
       <c r="F723" t="b">
         <v>1</v>
@@ -39209,15 +39271,15 @@
       <c r="J723" t="inlineStr"/>
       <c r="K723" t="inlineStr">
         <is>
-          <t>Wednesday 21 October 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L723" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M723" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N723" s="1" t="n">
@@ -39232,12 +39294,12 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Discovery C7</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C7</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2552/overview/9f47273b-291d-4328-a49e-a038eff65f0d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2550/overview/5cbb2d13-74bb-41b1-be19-005376930f80</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -39282,21 +39344,21 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>Ofgem Strategic Innovation Fund Discovery C7</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2579/overview/3eaba59f-330d-45f6-a406-78067a71bb70</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2552/overview/9f47273b-291d-4328-a49e-a038eff65f0d</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>2026-09-19 13:39</t>
+          <t>2026-09-18 14:02</t>
         </is>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284.56875</v>
+        <v>46283.58472222222</v>
       </c>
       <c r="F725" t="b">
         <v>1</v>
@@ -39309,15 +39371,15 @@
       <c r="J725" t="inlineStr"/>
       <c r="K725" t="inlineStr">
         <is>
-          <t>Tuesday 1 December 2026 11:00am</t>
+          <t>Wednesday 21 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L725" s="1" t="n">
-        <v>46357.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M725" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N725" s="1" t="n">
@@ -39332,21 +39394,21 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>CfI: Counter UAS Demonstrations in Prison Environments</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2570/overview/f33d0d62-4658-43fd-ae3d-b6362ebff0f0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2579/overview/3eaba59f-330d-45f6-a406-78067a71bb70</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>2026-09-24 14:35</t>
+          <t>2026-09-19 13:39</t>
         </is>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46289.60763888889</v>
+        <v>46284.56875</v>
       </c>
       <c r="F726" t="b">
         <v>1</v>
@@ -39359,19 +39421,19 @@
       <c r="J726" t="inlineStr"/>
       <c r="K726" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Tuesday 1 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L726" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>£80,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N726" s="1" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="727">
@@ -39382,12 +39444,12 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Frontier AI: SME Champions, Phase 1</t>
+          <t>CfI: Counter UAS Demonstrations in Prison Environments</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2584/overview/4c7afb5d-4572-4ef2-9507-73ef2dec8ec8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2570/overview/f33d0d62-4658-43fd-ae3d-b6362ebff0f0</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -39409,15 +39471,15 @@
       <c r="J727" t="inlineStr"/>
       <c r="K727" t="inlineStr">
         <is>
-          <t>Wednesday 11 November 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L727" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M727" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£80,000</t>
         </is>
       </c>
       <c r="N727" s="1" t="n">
@@ -39432,21 +39494,21 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Efficient, Structured and Controllable AI Systems</t>
+          <t>Frontier AI: SME Champions, Phase 1</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2582/overview/9fdb47a5-011c-4c47-ac5e-c426e295fe89</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2584/overview/4c7afb5d-4572-4ef2-9507-73ef2dec8ec8</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>2026-09-25 14:56</t>
+          <t>2026-09-24 14:35</t>
         </is>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46290.62222222222</v>
+        <v>46289.60763888889</v>
       </c>
       <c r="F728" t="b">
         <v>1</v>
@@ -39459,15 +39521,15 @@
       <c r="J728" t="inlineStr"/>
       <c r="K728" t="inlineStr">
         <is>
-          <t>Wednesday 18 November 2026 11:00am</t>
+          <t>Wednesday 11 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L728" s="1" t="n">
-        <v>46344.45833333334</v>
+        <v>46337.45833333334</v>
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N728" s="1" t="n">
@@ -39482,21 +39544,21 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>UK-Germany Bilateral Collaborative R&amp;D: Round 5</t>
+          <t>Efficient, Structured and Controllable AI Systems</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2583/overview/852abf67-ada4-49d3-b512-cf7c5ec6ac71</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2582/overview/9fdb47a5-011c-4c47-ac5e-c426e295fe89</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-25 14:56</t>
         </is>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46293.74652777778</v>
+        <v>46290.62222222222</v>
       </c>
       <c r="F729" t="b">
         <v>1</v>
@@ -39509,15 +39571,15 @@
       <c r="J729" t="inlineStr"/>
       <c r="K729" t="inlineStr">
         <is>
-          <t>Tuesday 1 December 2026 11:00am</t>
+          <t>Wednesday 18 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L729" s="1" t="n">
-        <v>46357.45833333334</v>
+        <v>46344.45833333334</v>
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>£350,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N729" s="1" t="n">
@@ -39532,21 +39594,21 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>CfI: Battery innovation for dual use &amp; defence Phase 1</t>
+          <t>UK-Germany Bilateral Collaborative R&amp;D: Round 5</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2587/overview/aafc825c-421e-47ea-bd56-d5d1cd50e513</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2583/overview/852abf67-ada4-49d3-b512-cf7c5ec6ac71</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>2026-09-29 16:18</t>
+          <t>2026-09-28 17:55</t>
         </is>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46294.67916666667</v>
+        <v>46293.74652777778</v>
       </c>
       <c r="F730" t="b">
         <v>1</v>
@@ -39559,15 +39621,15 @@
       <c r="J730" t="inlineStr"/>
       <c r="K730" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Tuesday 1 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L730" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="M730" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£350,000</t>
         </is>
       </c>
       <c r="N730" s="1" t="n">
@@ -39582,21 +39644,21 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Engineering Biology Investor Partnerships Round 1</t>
+          <t>CfI: Battery innovation for dual use &amp; defence Phase 1</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2580/overview/8881af18-31f4-4db3-9483-cbb047163164</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2587/overview/aafc825c-421e-47ea-bd56-d5d1cd50e513</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2026-10-01 16:50</t>
+          <t>2026-09-29 16:18</t>
         </is>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46296.70138888889</v>
+        <v>46294.67916666667</v>
       </c>
       <c r="F731" t="b">
         <v>1</v>
@@ -39609,19 +39671,19 @@
       <c r="J731" t="inlineStr"/>
       <c r="K731" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L731" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M731" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N731" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="732">
@@ -39632,21 +39694,21 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>MDI Programme Innovation and Scale-up Hub</t>
+          <t>Engineering Biology Investor Partnerships Round 1</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2588/overview/acbd9666-c1df-4635-b86f-fa426100c876</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2580/overview/8881af18-31f4-4db3-9483-cbb047163164</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>2026-10-03 14:31</t>
+          <t>2026-10-01 16:50</t>
         </is>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298.60486111111</v>
+        <v>46296.70138888889</v>
       </c>
       <c r="F732" t="b">
         <v>1</v>
@@ -39659,15 +39721,15 @@
       <c r="J732" t="inlineStr"/>
       <c r="K732" t="inlineStr">
         <is>
-          <t>Wednesday 18 November 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L732" s="1" t="n">
-        <v>46344.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M732" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N732" s="1" t="n">
@@ -39682,21 +39744,21 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Eureka collaborative R&amp;D: Globalstars Japan 2027</t>
+          <t>MDI Programme Innovation and Scale-up Hub</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2586/overview/d9e61ae4-6e56-4f38-9206-5d91ef98c916</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2588/overview/acbd9666-c1df-4635-b86f-fa426100c876</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>2026-10-05 19:06</t>
+          <t>2026-10-03 14:31</t>
         </is>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46300.79583333333</v>
+        <v>46298.60486111111</v>
       </c>
       <c r="F733" t="b">
         <v>1</v>
@@ -39709,15 +39771,15 @@
       <c r="J733" t="inlineStr"/>
       <c r="K733" t="inlineStr">
         <is>
-          <t>Wednesday 20 January 2027 11:00am</t>
+          <t>Wednesday 18 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L733" s="1" t="n">
-        <v>46407.45833333334</v>
+        <v>46344.45833333334</v>
       </c>
       <c r="M733" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N733" s="1" t="n">
@@ -39732,12 +39794,12 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Sustainable Medicines Manufacturing Innovation: CR&amp;D Round 2</t>
+          <t>Eureka collaborative R&amp;D: Globalstars Japan 2027</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2560/overview/45acacd5-746b-46ee-8051-d764f929cca3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2586/overview/d9e61ae4-6e56-4f38-9206-5d91ef98c916</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -39759,15 +39821,15 @@
       <c r="J734" t="inlineStr"/>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 20 January 2027 11:00am</t>
         </is>
       </c>
       <c r="L734" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46407.45833333334</v>
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N734" s="1" t="n">
@@ -39782,12 +39844,12 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Investor Partnerships – Battery Innovation Programme</t>
+          <t>Sustainable Medicines Manufacturing Innovation: CR&amp;D Round 2</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2595/overview/f2b849f6-0fb3-4012-be1b-a41813c93085</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2560/overview/45acacd5-746b-46ee-8051-d764f929cca3</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -39809,15 +39871,15 @@
       <c r="J735" t="inlineStr"/>
       <c r="K735" t="inlineStr">
         <is>
-          <t>Wednesday 25 November 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L735" s="1" t="n">
-        <v>46351.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M735" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N735" s="1" t="n">
@@ -39832,12 +39894,12 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 12</t>
+          <t>Investor Partnerships – Battery Innovation Programme</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2591/overview/b66dd413-9894-4fc4-a6c9-cced53367568</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2595/overview/f2b849f6-0fb3-4012-be1b-a41813c93085</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -39859,15 +39921,15 @@
       <c r="J736" t="inlineStr"/>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Wednesday 11 November 2026 11:00am</t>
+          <t>Wednesday 25 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L736" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46351.45833333334</v>
       </c>
       <c r="M736" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N736" s="1" t="n">
@@ -39882,21 +39944,21 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Operational Systems</t>
+          <t>ADOPT Facilitator Support Grant: Round 12</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2599/overview/1931f35c-87fe-4b6a-a718-a61a2d00e86a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2591/overview/b66dd413-9894-4fc4-a6c9-cced53367568</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2026-10-06 16:27</t>
+          <t>2026-10-05 19:06</t>
         </is>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46301.68541666667</v>
+        <v>46300.79583333333</v>
       </c>
       <c r="F737" t="b">
         <v>1</v>
@@ -39909,15 +39971,15 @@
       <c r="J737" t="inlineStr"/>
       <c r="K737" t="inlineStr">
         <is>
-          <t>Tuesday 8 December 2026 11:00am</t>
+          <t>Wednesday 11 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L737" s="1" t="n">
-        <v>46364.45833333334</v>
+        <v>46337.45833333334</v>
       </c>
       <c r="M737" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N737" s="1" t="n">
@@ -39932,12 +39994,12 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Decision Critical Systems</t>
+          <t>BridgeAI Deployment Catalyst: AI for Operational Systems</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2598/overview/cfb35198-55fc-4aad-afa1-86a260bfaddf</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2599/overview/1931f35c-87fe-4b6a-a718-a61a2d00e86a</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -39982,12 +40044,12 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Assurance and Compliance</t>
+          <t>BridgeAI Deployment Catalyst: AI for Decision Critical Systems</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2597/overview/7ec02a95-73e5-4928-8104-67a9f1b279e3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2598/overview/cfb35198-55fc-4aad-afa1-86a260bfaddf</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -40032,21 +40094,21 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>FOAK Builder: Programme Entry Expression of Interest</t>
+          <t>BridgeAI Deployment Catalyst: AI for Assurance and Compliance</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2600/overview/0c422454-a8af-4c24-a74a-565426f42395</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2597/overview/7ec02a95-73e5-4928-8104-67a9f1b279e3</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-06 16:27</t>
         </is>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46302.71527777778</v>
+        <v>46301.68541666667</v>
       </c>
       <c r="F740" t="b">
         <v>1</v>
@@ -40059,19 +40121,19 @@
       <c r="J740" t="inlineStr"/>
       <c r="K740" t="inlineStr">
         <is>
-          <t>Thursday 5 November 2026 11:00am</t>
+          <t>Tuesday 8 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L740" s="1" t="n">
-        <v>46331.45833333334</v>
+        <v>46364.45833333334</v>
       </c>
       <c r="M740" t="inlineStr">
         <is>
-          <t>£100.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N740" s="1" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="741">
@@ -40082,21 +40144,21 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 10</t>
+          <t>FOAK Builder: Programme Entry Expression of Interest</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2596/overview/31f0a768-2a9a-405d-b0a4-83a8c5b395c0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2600/overview/0c422454-a8af-4c24-a74a-565426f42395</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>2026-10-08 17:07</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46303.71319444444</v>
+        <v>46302.71527777778</v>
       </c>
       <c r="F741" t="b">
         <v>1</v>
@@ -40109,15 +40171,15 @@
       <c r="J741" t="inlineStr"/>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Thursday 5 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46331.45833333334</v>
       </c>
       <c r="M741" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£100.0 million</t>
         </is>
       </c>
       <c r="N741" s="1" t="n">
@@ -40132,21 +40194,21 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Growth Cohorts: Next-gen low carbon concrete cohort entry Round 2</t>
+          <t>Full ADOPT Grant: Round 10</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2602/overview/607351e2-798f-450b-b77d-3131912bcbef</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2596/overview/31f0a768-2a9a-405d-b0a4-83a8c5b395c0</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-08 17:07</t>
         </is>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46309.61805555555</v>
+        <v>46303.71319444444</v>
       </c>
       <c r="F742" t="b">
         <v>1</v>
@@ -40167,11 +40229,11 @@
       </c>
       <c r="M742" t="inlineStr">
         <is>
-          <t>£54,400</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N742" s="1" t="n">
-        <v>46309</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="743">
@@ -40182,21 +40244,21 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 - 2027 Round 4</t>
+          <t>Growth Cohorts: Next-gen low carbon concrete cohort entry Round 2</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2605/overview/4b82d27a-2794-457c-8dc7-7ec4f6911c84</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2602/overview/607351e2-798f-450b-b77d-3131912bcbef</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2026-10-19 16:45</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46314.69791666666</v>
+        <v>46309.61805555555</v>
       </c>
       <c r="F743" t="b">
         <v>1</v>
@@ -40209,13 +40271,17 @@
       <c r="J743" t="inlineStr"/>
       <c r="K743" t="inlineStr">
         <is>
-          <t>Wednesday 27 January 2027 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L743" s="1" t="n">
-        <v>46414.45833333334</v>
-      </c>
-      <c r="M743" t="inlineStr"/>
+        <v>46358.45833333334</v>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>£54,400</t>
+        </is>
+      </c>
       <c r="N743" s="1" t="n">
         <v>46309</v>
       </c>
@@ -40228,21 +40294,21 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Healthy Soils and Water for a Sustainable Environment</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 - 2027 Round 4</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2605/overview/4b82d27a-2794-457c-8dc7-7ec4f6911c84</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-19 16:45</t>
         </is>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46317.61736111111</v>
+        <v>46314.69791666666</v>
       </c>
       <c r="F744" t="b">
         <v>1</v>
@@ -40255,18 +40321,64 @@
       <c r="J744" t="inlineStr"/>
       <c r="K744" t="inlineStr">
         <is>
+          <t>Wednesday 27 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L744" s="1" t="n">
+        <v>46414.45833333334</v>
+      </c>
+      <c r="M744" t="inlineStr"/>
+      <c r="N744" s="1" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Healthy Soils and Water for a Sustainable Environment</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:49</t>
+        </is>
+      </c>
+      <c r="E745" s="1" t="n">
+        <v>46317.61736111111</v>
+      </c>
+      <c r="F745" t="b">
+        <v>1</v>
+      </c>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="b">
+        <v>0</v>
+      </c>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
           <t>Thursday 28 January 2027 11:00am</t>
         </is>
       </c>
-      <c r="L744" s="1" t="n">
+      <c r="L745" s="1" t="n">
         <v>46415.45833333334</v>
       </c>
-      <c r="M744" t="inlineStr">
+      <c r="M745" t="inlineStr">
         <is>
           <t>£5.0 million</t>
         </is>
       </c>
-      <c r="N744" s="1" t="n">
+      <c r="N745" s="1" t="n">
         <v>46316</v>
       </c>
     </row>
@@ -40308,10 +40420,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C2" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3">
@@ -40334,10 +40446,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C4" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1114,21 +1114,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Secure Innovation Security Reviews</t>
+          <t>iX Challenge: Systemic capture and analysis of structural condition data</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/secure-innovation-security-review/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-systemic-capture-and-analysis-of-structural-condition-data/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-23 14:29</t>
+          <t>2026-10-24 13:41</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318.60347222222</v>
+        <v>46319.57013888889</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1147,17 +1147,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>31/01/2027                              12:00</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>46418.5</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>£315,000</t>
-        </is>
-      </c>
+          <t>04/12/2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" s="1" t="n">
         <v>46316</v>
       </c>
@@ -1165,26 +1159,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthy Soils and Water for a Sustainable Environment</t>
+          <t>Secure Innovation Security Reviews</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/secure-innovation-security-review/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:29</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317.61736111111</v>
+        <v>46318.60347222222</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1193,19 +1187,25 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>46318</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Thursday 28 January 2027 11:00am</t>
+          <t>31/01/2027                              12:00</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46415.45833333334</v>
+        <v>46418.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£315,000</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1215,26 +1215,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
+          <t>Healthy Soils and Water for a Sustainable Environment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:43</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316.61319444444</v>
+        <v>46317.61736111111</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1243,23 +1243,19 @@
       <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>46314</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>Thursday 28 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>46415.45833333334</v>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N4" s="1" t="n">
@@ -1274,12 +1270,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
+          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1299,21 +1295,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N5" s="1" t="n">
@@ -1328,12 +1324,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1353,20 +1349,74 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:43</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46316.61319444444</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>01/12/2026</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" s="1" t="n">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="1" t="n">
         <v>46316</v>
       </c>
     </row>
@@ -1414,10 +1464,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2425,7 +2475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N745"/>
+  <dimension ref="A1:N746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28157,26 +28207,26 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>iX Challenge: Systemic capture and analysis of structural condition data</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-systemic-capture-and-analysis-of-structural-condition-data/</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-10-24 13:41</t>
         </is>
       </c>
       <c r="E500" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46319.57013888889</v>
       </c>
       <c r="F500" t="b">
         <v>1</v>
@@ -28185,23 +28235,23 @@
       <c r="H500" t="b">
         <v>0</v>
       </c>
-      <c r="I500" t="inlineStr"/>
-      <c r="J500" t="inlineStr"/>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="J500" s="1" t="n">
+        <v>46318</v>
+      </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L500" s="1" t="n">
-        <v>45966.45833333334</v>
-      </c>
-      <c r="M500" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+          <t>04/12/2026</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
       <c r="N500" s="1" t="n">
-        <v>45819</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="501">
@@ -28212,12 +28262,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -28239,15 +28289,15 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L501" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N501" s="1" t="n">
@@ -28262,12 +28312,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -28289,15 +28339,15 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L502" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N502" s="1" t="n">
@@ -28312,12 +28362,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -28347,7 +28397,7 @@
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N503" s="1" t="n">
@@ -28362,12 +28412,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -28389,15 +28439,15 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L504" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N504" s="1" t="n">
@@ -28412,12 +28462,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -28439,13 +28489,17 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L505" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M505" t="inlineStr"/>
+        <v>45904.45833333334</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N505" s="1" t="n">
         <v>45819</v>
       </c>
@@ -28458,12 +28512,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -28485,17 +28539,13 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L506" s="1" t="n">
-        <v>45840.45833333334</v>
-      </c>
-      <c r="M506" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M506" t="inlineStr"/>
       <c r="N506" s="1" t="n">
         <v>45819</v>
       </c>
@@ -28508,12 +28558,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -28535,15 +28585,15 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L507" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N507" s="1" t="n">
@@ -28558,12 +28608,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -28608,12 +28658,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -28635,15 +28685,15 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L509" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N509" s="1" t="n">
@@ -28658,12 +28708,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -28685,15 +28735,15 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L510" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N510" s="1" t="n">
@@ -28708,12 +28758,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -28735,15 +28785,15 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L511" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N511" s="1" t="n">
@@ -28758,12 +28808,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -28808,12 +28858,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -28835,15 +28885,15 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L513" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N513" s="1" t="n">
@@ -28858,12 +28908,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -28893,7 +28943,7 @@
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N514" s="1" t="n">
@@ -28908,12 +28958,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -28935,15 +28985,15 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L515" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N515" s="1" t="n">
@@ -28958,12 +29008,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -28985,15 +29035,15 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L516" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N516" s="1" t="n">
@@ -29008,12 +29058,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -29043,7 +29093,7 @@
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N517" s="1" t="n">
@@ -29058,12 +29108,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -29085,15 +29135,15 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L518" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M518" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N518" s="1" t="n">
@@ -29108,12 +29158,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -29158,12 +29208,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -29185,15 +29235,15 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L520" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N520" s="1" t="n">
@@ -29208,12 +29258,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -29235,15 +29285,15 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L521" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N521" s="1" t="n">
@@ -29258,12 +29308,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -29285,11 +29335,17 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L522" t="inlineStr"/>
-      <c r="M522" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L522" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N522" s="1" t="n">
         <v>45819</v>
       </c>
@@ -29302,12 +29358,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -29346,21 +29402,21 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E524" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F524" t="b">
         <v>1</v>
@@ -29373,17 +29429,11 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L524" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M524" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
       <c r="N524" s="1" t="n">
         <v>45819</v>
       </c>
@@ -29396,21 +29446,21 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E525" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F525" t="b">
         <v>1</v>
@@ -29423,19 +29473,19 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L525" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N525" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="526">
@@ -29446,12 +29496,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -29481,7 +29531,7 @@
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N526" s="1" t="n">
@@ -29496,21 +29546,21 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E527" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F527" t="b">
         <v>1</v>
@@ -29523,19 +29573,19 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L527" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N527" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="528">
@@ -29546,21 +29596,21 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E528" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F528" t="b">
         <v>1</v>
@@ -29573,15 +29623,15 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L528" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N528" s="1" t="n">
@@ -29596,12 +29646,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -29623,13 +29673,17 @@
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L529" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M529" t="inlineStr"/>
+        <v>45875.45833333334</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N529" s="1" t="n">
         <v>45840</v>
       </c>
@@ -29642,21 +29696,21 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E530" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F530" t="b">
         <v>1</v>
@@ -29669,19 +29723,15 @@
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L530" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M530" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M530" t="inlineStr"/>
       <c r="N530" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="531">
@@ -29692,12 +29742,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -29742,12 +29792,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -29792,12 +29842,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -29819,15 +29869,15 @@
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L533" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N533" s="1" t="n">
@@ -29842,21 +29892,21 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E534" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F534" t="b">
         <v>1</v>
@@ -29869,15 +29919,15 @@
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L534" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M534" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N534" s="1" t="n">
@@ -29892,12 +29942,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -29919,15 +29969,15 @@
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L535" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M535" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N535" s="1" t="n">
@@ -29942,12 +29992,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -29977,7 +30027,7 @@
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N536" s="1" t="n">
@@ -29992,21 +30042,21 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E537" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F537" t="b">
         <v>1</v>
@@ -30019,19 +30069,19 @@
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L537" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M537" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N537" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="538">
@@ -30042,21 +30092,21 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E538" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F538" t="b">
         <v>1</v>
@@ -30069,19 +30119,19 @@
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L538" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N538" s="1" t="n">
-        <v>45875</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="539">
@@ -30092,21 +30142,21 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E539" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F539" t="b">
         <v>1</v>
@@ -30119,19 +30169,19 @@
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L539" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M539" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N539" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="540">
@@ -30142,12 +30192,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -30177,7 +30227,7 @@
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N540" s="1" t="n">
@@ -30192,12 +30242,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -30227,7 +30277,7 @@
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N541" s="1" t="n">
@@ -30242,21 +30292,21 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E542" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F542" t="b">
         <v>1</v>
@@ -30269,19 +30319,19 @@
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L542" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N542" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="543">
@@ -30292,21 +30342,21 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E543" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F543" t="b">
         <v>1</v>
@@ -30319,11 +30369,11 @@
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L543" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M543" t="inlineStr">
         <is>
@@ -30331,7 +30381,7 @@
         </is>
       </c>
       <c r="N543" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="544">
@@ -30342,21 +30392,21 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E544" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F544" t="b">
         <v>1</v>
@@ -30369,13 +30419,17 @@
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L544" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M544" t="inlineStr"/>
+        <v>45945.45833333334</v>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N544" s="1" t="n">
         <v>45896</v>
       </c>
@@ -30388,21 +30442,21 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E545" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F545" t="b">
         <v>1</v>
@@ -30415,17 +30469,13 @@
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L545" s="1" t="n">
-        <v>45966.45833333334</v>
-      </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>£3.0 million</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M545" t="inlineStr"/>
       <c r="N545" s="1" t="n">
         <v>45896</v>
       </c>
@@ -30438,21 +30488,21 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E546" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F546" t="b">
         <v>1</v>
@@ -30465,19 +30515,19 @@
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L546" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N546" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="547">
@@ -30488,21 +30538,21 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E547" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F547" t="b">
         <v>1</v>
@@ -30515,15 +30565,15 @@
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L547" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N547" s="1" t="n">
@@ -30538,21 +30588,21 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E548" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F548" t="b">
         <v>1</v>
@@ -30565,19 +30615,19 @@
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L548" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N548" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="549">
@@ -30588,21 +30638,21 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E549" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F549" t="b">
         <v>1</v>
@@ -30615,15 +30665,15 @@
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Tuesday 28 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L549" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45958.45833333334</v>
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N549" s="1" t="n">
@@ -30638,21 +30688,21 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E550" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F550" t="b">
         <v>1</v>
@@ -30665,17 +30715,19 @@
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L550" t="inlineStr"/>
+          <t>Wednesday 15 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L550" s="1" t="n">
+        <v>45945.45833333334</v>
+      </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N550" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="551">
@@ -30686,21 +30738,21 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E551" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F551" t="b">
         <v>1</v>
@@ -30713,15 +30765,13 @@
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L551" s="1" t="n">
-        <v>45995.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr"/>
       <c r="M551" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N551" s="1" t="n">
@@ -30736,21 +30786,21 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E552" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F552" t="b">
         <v>1</v>
@@ -30763,15 +30813,15 @@
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L552" s="1" t="n">
-        <v>45964.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N552" s="1" t="n">
@@ -30786,21 +30836,21 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E553" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F553" t="b">
         <v>1</v>
@@ -30813,15 +30863,15 @@
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L553" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N553" s="1" t="n">
@@ -30836,21 +30886,21 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E554" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F554" t="b">
         <v>1</v>
@@ -30863,19 +30913,19 @@
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L554" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N554" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="555">
@@ -30886,21 +30936,21 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E555" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F555" t="b">
         <v>1</v>
@@ -30913,19 +30963,19 @@
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L555" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N555" s="1" t="n">
-        <v>45931</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="556">
@@ -30936,21 +30986,21 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E556" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F556" t="b">
         <v>1</v>
@@ -30963,19 +31013,19 @@
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L556" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46043.45833333334</v>
       </c>
       <c r="M556" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N556" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="557">
@@ -30986,21 +31036,21 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E557" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F557" t="b">
         <v>1</v>
@@ -31013,13 +31063,17 @@
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L557" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M557" t="inlineStr"/>
+        <v>45987.45833333334</v>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>£250,000</t>
+        </is>
+      </c>
       <c r="N557" s="1" t="n">
         <v>45938</v>
       </c>
@@ -31032,21 +31086,21 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E558" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F558" t="b">
         <v>1</v>
@@ -31059,19 +31113,15 @@
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L558" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M558" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M558" t="inlineStr"/>
       <c r="N558" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="559">
@@ -31082,12 +31132,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -31117,7 +31167,7 @@
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N559" s="1" t="n">
@@ -31132,21 +31182,21 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E560" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F560" t="b">
         <v>1</v>
@@ -31159,15 +31209,15 @@
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L560" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N560" s="1" t="n">
@@ -31182,21 +31232,21 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E561" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F561" t="b">
         <v>1</v>
@@ -31217,7 +31267,7 @@
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N561" s="1" t="n">
@@ -31232,21 +31282,21 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E562" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F562" t="b">
         <v>1</v>
@@ -31259,15 +31309,15 @@
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L562" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N562" s="1" t="n">
@@ -31282,12 +31332,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -31317,7 +31367,7 @@
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N563" s="1" t="n">
@@ -31332,21 +31382,21 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E564" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F564" t="b">
         <v>1</v>
@@ -31359,13 +31409,17 @@
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L564" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M564" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N564" s="1" t="n">
         <v>45945</v>
       </c>
@@ -31378,21 +31432,21 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E565" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F565" t="b">
         <v>1</v>
@@ -31405,19 +31459,15 @@
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L565" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M565" t="inlineStr">
-        <is>
-          <t>£1.0 million</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M565" t="inlineStr"/>
       <c r="N565" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="566">
@@ -31428,12 +31478,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -31463,7 +31513,7 @@
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N566" s="1" t="n">
@@ -31478,21 +31528,21 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E567" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F567" t="b">
         <v>1</v>
@@ -31513,7 +31563,7 @@
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N567" s="1" t="n">
@@ -31528,21 +31578,21 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E568" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F568" t="b">
         <v>1</v>
@@ -31555,15 +31605,15 @@
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L568" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M568" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N568" s="1" t="n">
@@ -31578,21 +31628,21 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E569" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F569" t="b">
         <v>1</v>
@@ -31605,15 +31655,15 @@
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L569" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N569" s="1" t="n">
@@ -31628,21 +31678,21 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E570" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F570" t="b">
         <v>1</v>
@@ -31655,19 +31705,19 @@
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L570" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N570" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="571">
@@ -31678,21 +31728,21 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E571" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F571" t="b">
         <v>1</v>
@@ -31705,15 +31755,15 @@
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L571" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M571" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N571" s="1" t="n">
@@ -31728,12 +31778,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -31755,15 +31805,15 @@
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L572" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M572" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N572" s="1" t="n">
@@ -31778,21 +31828,21 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E573" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F573" t="b">
         <v>1</v>
@@ -31805,19 +31855,19 @@
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L573" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N573" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="574">
@@ -31828,12 +31878,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -31863,7 +31913,7 @@
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N574" s="1" t="n">
@@ -31878,12 +31928,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -31905,13 +31955,17 @@
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L575" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M575" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>£4.0 million</t>
+        </is>
+      </c>
       <c r="N575" s="1" t="n">
         <v>45966</v>
       </c>
@@ -31924,21 +31978,21 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E576" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F576" t="b">
         <v>1</v>
@@ -31951,17 +32005,13 @@
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L576" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M576" t="inlineStr">
-        <is>
-          <t>£750,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M576" t="inlineStr"/>
       <c r="N576" s="1" t="n">
         <v>45966</v>
       </c>
@@ -31974,21 +32024,21 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E577" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F577" t="b">
         <v>1</v>
@@ -32001,19 +32051,19 @@
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L577" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M577" t="inlineStr">
         <is>
-          <t>£75,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N577" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="578">
@@ -32024,21 +32074,21 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E578" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F578" t="b">
         <v>1</v>
@@ -32059,7 +32109,7 @@
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N578" s="1" t="n">
@@ -32074,21 +32124,21 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F579" t="b">
         <v>1</v>
@@ -32101,19 +32151,19 @@
       <c r="J579" t="inlineStr"/>
       <c r="K579" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L579" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M579" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N579" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="580">
@@ -32124,21 +32174,21 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F580" t="b">
         <v>1</v>
@@ -32151,15 +32201,15 @@
       <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L580" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N580" s="1" t="n">
@@ -32174,21 +32224,21 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F581" t="b">
         <v>1</v>
@@ -32201,19 +32251,19 @@
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L581" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M581" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N581" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="582">
@@ -32224,12 +32274,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -32251,15 +32301,15 @@
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L582" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N582" s="1" t="n">
@@ -32274,21 +32324,21 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F583" t="b">
         <v>1</v>
@@ -32301,19 +32351,19 @@
       <c r="J583" t="inlineStr"/>
       <c r="K583" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L583" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N583" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="584">
@@ -32324,12 +32374,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -32359,7 +32409,7 @@
       </c>
       <c r="M584" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N584" s="1" t="n">
@@ -32374,12 +32424,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -32409,7 +32459,7 @@
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N585" s="1" t="n">
@@ -32424,12 +32474,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -32451,15 +32501,15 @@
       <c r="J586" t="inlineStr"/>
       <c r="K586" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L586" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M586" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N586" s="1" t="n">
@@ -32474,12 +32524,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -32501,15 +32551,15 @@
       <c r="J587" t="inlineStr"/>
       <c r="K587" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L587" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N587" s="1" t="n">
@@ -32524,21 +32574,21 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F588" t="b">
         <v>1</v>
@@ -32551,19 +32601,19 @@
       <c r="J588" t="inlineStr"/>
       <c r="K588" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L588" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N588" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="589">
@@ -32574,21 +32624,21 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F589" t="b">
         <v>1</v>
@@ -32601,19 +32651,19 @@
       <c r="J589" t="inlineStr"/>
       <c r="K589" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L589" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N589" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="590">
@@ -32624,21 +32674,21 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46042.35</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F590" t="b">
         <v>1</v>
@@ -32651,15 +32701,15 @@
       <c r="J590" t="inlineStr"/>
       <c r="K590" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L590" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N590" s="1" t="n">
@@ -32674,21 +32724,21 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46042.35</v>
       </c>
       <c r="F591" t="b">
         <v>1</v>
@@ -32701,19 +32751,19 @@
       <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L591" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N591" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="592">
@@ -32724,21 +32774,21 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F592" t="b">
         <v>1</v>
@@ -32751,19 +32801,19 @@
       <c r="J592" t="inlineStr"/>
       <c r="K592" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L592" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N592" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="593">
@@ -32774,12 +32824,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -32809,7 +32859,7 @@
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N593" s="1" t="n">
@@ -32824,21 +32874,21 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F594" t="b">
         <v>1</v>
@@ -32851,15 +32901,15 @@
       <c r="J594" t="inlineStr"/>
       <c r="K594" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L594" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N594" s="1" t="n">
@@ -32874,21 +32924,21 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F595" t="b">
         <v>1</v>
@@ -32901,15 +32951,15 @@
       <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L595" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N595" s="1" t="n">
@@ -32924,12 +32974,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -32951,13 +33001,17 @@
       <c r="J596" t="inlineStr"/>
       <c r="K596" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L596" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M596" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N596" s="1" t="n">
         <v>46050</v>
       </c>
@@ -32970,12 +33024,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -33016,21 +33070,21 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F598" t="b">
         <v>1</v>
@@ -33043,19 +33097,15 @@
       <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L598" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M598" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M598" t="inlineStr"/>
       <c r="N598" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="599">
@@ -33066,21 +33116,21 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F599" t="b">
         <v>1</v>
@@ -33093,19 +33143,19 @@
       <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L599" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N599" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="600">
@@ -33116,12 +33166,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -33143,15 +33193,15 @@
       <c r="J600" t="inlineStr"/>
       <c r="K600" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L600" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N600" s="1" t="n">
@@ -33166,12 +33216,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -33201,7 +33251,7 @@
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N601" s="1" t="n">
@@ -33216,21 +33266,21 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F602" t="b">
         <v>1</v>
@@ -33243,15 +33293,15 @@
       <c r="J602" t="inlineStr"/>
       <c r="K602" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L602" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N602" s="1" t="n">
@@ -33266,21 +33316,21 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F603" t="b">
         <v>1</v>
@@ -33301,7 +33351,7 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N603" s="1" t="n">
@@ -33316,21 +33366,21 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F604" t="b">
         <v>1</v>
@@ -33343,19 +33393,19 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L604" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N604" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="605">
@@ -33366,21 +33416,21 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F605" t="b">
         <v>1</v>
@@ -33393,15 +33443,15 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L605" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N605" s="1" t="n">
@@ -33416,12 +33466,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -33451,7 +33501,7 @@
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N606" s="1" t="n">
@@ -33466,21 +33516,21 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F607" t="b">
         <v>1</v>
@@ -33493,19 +33543,19 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L607" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N607" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="608">
@@ -33516,21 +33566,21 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>2026-03-03 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46084.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F608" t="b">
         <v>1</v>
@@ -33543,15 +33593,15 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L608" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N608" s="1" t="n">
@@ -33566,21 +33616,21 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F609" t="b">
         <v>1</v>
@@ -33593,19 +33643,19 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L609" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N609" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="610">
@@ -33616,12 +33666,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -33651,7 +33701,7 @@
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N610" s="1" t="n">
@@ -33666,12 +33716,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -33701,7 +33751,7 @@
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N611" s="1" t="n">
@@ -33716,21 +33766,21 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>AI Champions: Frontier AI Phase 1</t>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>2026-03-12 10:34</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46093.44027777778</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F612" t="b">
         <v>1</v>
@@ -33743,15 +33793,15 @@
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L612" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£15.0 million</t>
         </is>
       </c>
       <c r="N612" s="1" t="n">
@@ -33766,21 +33816,21 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Frontier AI Discovery</t>
+          <t>AI Champions: Frontier AI Phase 1</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-12 10:34</t>
         </is>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46093.44027777778</v>
       </c>
       <c r="F613" t="b">
         <v>1</v>
@@ -33793,15 +33843,15 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L613" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N613" s="1" t="n">
@@ -33816,12 +33866,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Secure Software for Resilient Growth</t>
+          <t>Frontier AI Discovery</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -33843,15 +33893,15 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L614" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N614" s="1" t="n">
@@ -33866,12 +33916,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+          <t>Secure Software for Resilient Growth</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -33893,15 +33943,15 @@
       <c r="J615" t="inlineStr"/>
       <c r="K615" t="inlineStr">
         <is>
-          <t>Wednesday 22 April 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L615" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N615" s="1" t="n">
@@ -33916,21 +33966,21 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Frontier AI Benchmarking Datasets</t>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>2026-03-23 10:49</t>
+          <t>2026-03-17 10:45</t>
         </is>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46104.45069444444</v>
+        <v>46098.44791666666</v>
       </c>
       <c r="F616" t="b">
         <v>1</v>
@@ -33943,19 +33993,19 @@
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 22 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L616" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="M616" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N616" s="1" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="617">
@@ -33966,21 +34016,21 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing: Labs of the Future</t>
+          <t>Frontier AI Benchmarking Datasets</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>2026-03-24 10:47</t>
+          <t>2026-03-23 10:49</t>
         </is>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46105.44930555556</v>
+        <v>46104.45069444444</v>
       </c>
       <c r="F617" t="b">
         <v>1</v>
@@ -34001,7 +34051,7 @@
       </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N617" s="1" t="n">
@@ -34016,12 +34066,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
+          <t>Medicines Manufacturing: Labs of the Future</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -34043,15 +34093,15 @@
       <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L618" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M618" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N618" s="1" t="n">
@@ -34066,12 +34116,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -34101,7 +34151,7 @@
       </c>
       <c r="M619" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N619" s="1" t="n">
@@ -34116,21 +34166,21 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>2026-03-26 10:49</t>
+          <t>2026-03-24 10:47</t>
         </is>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46107.45069444444</v>
+        <v>46105.44930555556</v>
       </c>
       <c r="F620" t="b">
         <v>1</v>
@@ -34143,19 +34193,19 @@
       <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L620" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M620" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N620" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="621">
@@ -34166,12 +34216,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -34216,12 +34266,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -34266,21 +34316,21 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>2026-03-27 10:43</t>
+          <t>2026-03-26 10:49</t>
         </is>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46108.44652777778</v>
+        <v>46107.45069444444</v>
       </c>
       <c r="F623" t="b">
         <v>1</v>
@@ -34293,15 +34343,15 @@
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L623" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M623" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N623" s="1" t="n">
@@ -34316,21 +34366,21 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
+          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>2026-03-28 10:27</t>
+          <t>2026-03-27 10:43</t>
         </is>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46109.43541666667</v>
+        <v>46108.44652777778</v>
       </c>
       <c r="F624" t="b">
         <v>1</v>
@@ -34343,15 +34393,15 @@
       <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr">
         <is>
-          <t>Friday 29 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L624" s="1" t="n">
-        <v>46171.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M624" t="inlineStr">
         <is>
-          <t>£14.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N624" s="1" t="n">
@@ -34366,21 +34416,21 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: industrial research</t>
+          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>2026-04-01 10:50</t>
+          <t>2026-03-28 10:27</t>
         </is>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46113.45138888889</v>
+        <v>46109.43541666667</v>
       </c>
       <c r="F625" t="b">
         <v>1</v>
@@ -34393,19 +34443,19 @@
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Friday 29 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L625" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£14.0 million</t>
         </is>
       </c>
       <c r="N625" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="626">
@@ -34416,12 +34466,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: feasibility studies</t>
+          <t>Future offshore wind technologies: industrial research</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -34451,7 +34501,7 @@
       </c>
       <c r="M626" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N626" s="1" t="n">
@@ -34466,12 +34516,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Solution Development for Advanced Connectivity Technologies</t>
+          <t>Future offshore wind technologies: feasibility studies</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -34493,15 +34543,15 @@
       <c r="J627" t="inlineStr"/>
       <c r="K627" t="inlineStr">
         <is>
-          <t>Wednesday 13 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L627" s="1" t="n">
-        <v>46155.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M627" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N627" s="1" t="n">
@@ -34516,12 +34566,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
+          <t>Solution Development for Advanced Connectivity Technologies</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -34543,15 +34593,15 @@
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 13 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L628" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="M628" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N628" s="1" t="n">
@@ -34566,21 +34616,21 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
+          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>2026-04-07 10:51</t>
+          <t>2026-04-01 10:50</t>
         </is>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46119.45208333333</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="F629" t="b">
         <v>1</v>
@@ -34593,15 +34643,15 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>Wednesday 20 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L629" s="1" t="n">
-        <v>46162.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M629" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N629" s="1" t="n">
@@ -34616,21 +34666,21 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 7</t>
+          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>2026-04-09 10:54</t>
+          <t>2026-04-07 10:51</t>
         </is>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46121.45416666667</v>
+        <v>46119.45208333333</v>
       </c>
       <c r="F630" t="b">
         <v>1</v>
@@ -34643,19 +34693,19 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 20 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L630" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="M630" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N630" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="631">
@@ -34666,21 +34716,21 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Full ADOPT Grant: Round 7</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>2026-04-11 10:30</t>
+          <t>2026-04-09 10:54</t>
         </is>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46123.4375</v>
+        <v>46121.45416666667</v>
       </c>
       <c r="F631" t="b">
         <v>1</v>
@@ -34693,13 +34743,15 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>Wednesday 1 July 2026 12:00pm</t>
-        </is>
-      </c>
-      <c r="L631" t="inlineStr"/>
+          <t>Wednesday 3 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L631" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
       <c r="M631" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N631" s="1" t="n">
@@ -34714,21 +34766,21 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Battery innovation feasibility studies round 2</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>2026-04-14 10:58</t>
+          <t>2026-04-11 10:30</t>
         </is>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46126.45694444444</v>
+        <v>46123.4375</v>
       </c>
       <c r="F632" t="b">
         <v>1</v>
@@ -34741,15 +34793,13 @@
       <c r="J632" t="inlineStr"/>
       <c r="K632" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L632" s="1" t="n">
-        <v>46169.45833333334</v>
-      </c>
+          <t>Wednesday 1 July 2026 12:00pm</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr"/>
       <c r="M632" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N632" s="1" t="n">
@@ -34764,12 +34814,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Battery innovation concept development round 2</t>
+          <t>Battery innovation feasibility studies round 2</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -34799,7 +34849,7 @@
       </c>
       <c r="M633" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N633" s="1" t="n">
@@ -34814,21 +34864,21 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 8</t>
+          <t>Battery innovation concept development round 2</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>2026-04-15 10:55</t>
+          <t>2026-04-14 10:58</t>
         </is>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46127.45486111111</v>
+        <v>46126.45694444444</v>
       </c>
       <c r="F634" t="b">
         <v>1</v>
@@ -34849,11 +34899,11 @@
       </c>
       <c r="M634" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N634" s="1" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="635">
@@ -34864,21 +34914,21 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
+          <t>ADOPT Facilitator Support Grant: Round 8</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>2026-04-18 10:35</t>
+          <t>2026-04-15 10:55</t>
         </is>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46130.44097222222</v>
+        <v>46127.45486111111</v>
       </c>
       <c r="F635" t="b">
         <v>1</v>
@@ -34891,15 +34941,15 @@
       <c r="J635" t="inlineStr"/>
       <c r="K635" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L635" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M635" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N635" s="1" t="n">
@@ -34914,21 +34964,21 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
+          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>2026-04-20 11:16</t>
+          <t>2026-04-18 10:35</t>
         </is>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46132.46944444445</v>
+        <v>46130.44097222222</v>
       </c>
       <c r="F636" t="b">
         <v>1</v>
@@ -34941,15 +34991,15 @@
       <c r="J636" t="inlineStr"/>
       <c r="K636" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L636" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M636" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N636" s="1" t="n">
@@ -34964,21 +35014,21 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation: CRD</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>2026-04-21 11:02</t>
+          <t>2026-04-20 11:16</t>
         </is>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46133.45972222222</v>
+        <v>46132.46944444445</v>
       </c>
       <c r="F637" t="b">
         <v>1</v>
@@ -34991,15 +35041,15 @@
       <c r="J637" t="inlineStr"/>
       <c r="K637" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L637" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M637" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N637" s="1" t="n">
@@ -35014,21 +35064,21 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
+          <t>Advanced manufacturing supply chain innovation: CRD</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>2026-04-22 11:00</t>
+          <t>2026-04-21 11:02</t>
         </is>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46133.45972222222</v>
       </c>
       <c r="F638" t="b">
         <v>1</v>
@@ -35041,13 +35091,19 @@
       <c r="J638" t="inlineStr"/>
       <c r="K638" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L638" t="inlineStr"/>
-      <c r="M638" t="inlineStr"/>
+          <t>Wednesday 10 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L638" s="1" t="n">
+        <v>46183.45833333334</v>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
       <c r="N638" s="1" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="639">
@@ -35058,21 +35114,21 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>2026-04-23 11:03</t>
+          <t>2026-04-22 11:00</t>
         </is>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46135.46041666667</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="F639" t="b">
         <v>1</v>
@@ -35085,17 +35141,11 @@
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L639" s="1" t="n">
-        <v>46183.45833333334</v>
-      </c>
-      <c r="M639" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr"/>
       <c r="N639" s="1" t="n">
         <v>46134</v>
       </c>
@@ -35108,21 +35158,21 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Dual-use aviation systems and autonomy</t>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>2026-04-28 11:42</t>
+          <t>2026-04-23 11:03</t>
         </is>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46140.4875</v>
+        <v>46135.46041666667</v>
       </c>
       <c r="F640" t="b">
         <v>1</v>
@@ -35135,15 +35185,15 @@
       <c r="J640" t="inlineStr"/>
       <c r="K640" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L640" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>£1.2 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N640" s="1" t="n">
@@ -35158,12 +35208,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Counter UAS Technologies</t>
+          <t>Dual-use aviation systems and autonomy</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -35208,21 +35258,21 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility studies Rd 2</t>
+          <t>Counter UAS Technologies</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2469/overview/63ad7c49-77d4-4e13-b07f-0078c28d718e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>2026-04-30 11:25</t>
+          <t>2026-04-28 11:42</t>
         </is>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46142.47569444445</v>
+        <v>46140.4875</v>
       </c>
       <c r="F642" t="b">
         <v>1</v>
@@ -35235,19 +35285,19 @@
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L642" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M642" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.2 million</t>
         </is>
       </c>
       <c r="N642" s="1" t="n">
-        <v>46141</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="643">
@@ -35258,21 +35308,21 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>CfI: Boosting fathers’ engagement to improve child outcomes</t>
+          <t>National Materials Innovation Programme: Feasibility studies Rd 2</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2458/overview/bd6562cf-e556-4860-9348-663db48bb1a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2469/overview/63ad7c49-77d4-4e13-b07f-0078c28d718e</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>2026-05-05 11:13</t>
+          <t>2026-04-30 11:25</t>
         </is>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46147.46736111111</v>
+        <v>46142.47569444445</v>
       </c>
       <c r="F643" t="b">
         <v>1</v>
@@ -35285,15 +35335,15 @@
       <c r="J643" t="inlineStr"/>
       <c r="K643" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L643" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M643" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N643" s="1" t="n">
@@ -35308,21 +35358,21 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Battery Innovation Programme: Battery skills initiatives</t>
+          <t>CfI: Boosting fathers’ engagement to improve child outcomes</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2449/overview/34dd1264-cf19-4a9b-90bf-755e413085a5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2458/overview/bd6562cf-e556-4860-9348-663db48bb1a8</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>2026-05-07 11:43</t>
+          <t>2026-05-05 11:13</t>
         </is>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46149.48819444444</v>
+        <v>46147.46736111111</v>
       </c>
       <c r="F644" t="b">
         <v>1</v>
@@ -35335,19 +35385,19 @@
       <c r="J644" t="inlineStr"/>
       <c r="K644" t="inlineStr">
         <is>
-          <t>Thursday 18 June 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L644" s="1" t="n">
-        <v>46191.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M644" t="inlineStr">
         <is>
-          <t>£1.2 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N644" s="1" t="n">
-        <v>46148</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="645">
@@ -35358,21 +35408,21 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>Battery Innovation Programme: Battery skills initiatives</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2472/overview/8d51ea8e-212a-4a55-8e32-3237f92a86f2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2449/overview/34dd1264-cf19-4a9b-90bf-755e413085a5</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>2026-05-09 10:53</t>
+          <t>2026-05-07 11:43</t>
         </is>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46151.45347222222</v>
+        <v>46149.48819444444</v>
       </c>
       <c r="F645" t="b">
         <v>1</v>
@@ -35385,15 +35435,15 @@
       <c r="J645" t="inlineStr"/>
       <c r="K645" t="inlineStr">
         <is>
-          <t>Wednesday 17 June 2026 11:00am</t>
+          <t>Thursday 18 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L645" s="1" t="n">
-        <v>46190.45833333334</v>
+        <v>46191.45833333334</v>
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£1.2 million</t>
         </is>
       </c>
       <c r="N645" s="1" t="n">
@@ -35408,12 +35458,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Solution Development for Advanced Connectivity Technologies: applications with academic partners</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2474/overview/7dec743d-f024-43d9-8bfc-62331c987d09</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2472/overview/8d51ea8e-212a-4a55-8e32-3237f92a86f2</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -35435,15 +35485,15 @@
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Wednesday 13 May 2026 11:00am</t>
+          <t>Wednesday 17 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L646" s="1" t="n">
-        <v>46155.45833333334</v>
+        <v>46190.45833333334</v>
       </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N646" s="1" t="n">
@@ -35458,21 +35508,21 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: FOAK26</t>
+          <t>Solution Development for Advanced Connectivity Technologies: applications with academic partners</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2475/overview/6fba05b0-d73b-4a33-886e-cb0950f1252a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2474/overview/7dec743d-f024-43d9-8bfc-62331c987d09</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>2026-05-12 11:50</t>
+          <t>2026-05-09 10:53</t>
         </is>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46154.49305555555</v>
+        <v>46151.45347222222</v>
       </c>
       <c r="F647" t="b">
         <v>1</v>
@@ -35485,15 +35535,15 @@
       <c r="J647" t="inlineStr"/>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 13 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L647" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>£210,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N647" s="1" t="n">
@@ -35508,21 +35558,21 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer Partnerships 6 (AKT 6)</t>
+          <t>Contracts for Innovation: FOAK26</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2473/overview/d9a164dd-2094-4590-baa7-a057279d80a3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2475/overview/6fba05b0-d73b-4a33-886e-cb0950f1252a</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>2026-05-16 10:59</t>
+          <t>2026-05-12 11:50</t>
         </is>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46158.45763888889</v>
+        <v>46154.49305555555</v>
       </c>
       <c r="F648" t="b">
         <v>1</v>
@@ -35535,19 +35585,19 @@
       <c r="J648" t="inlineStr"/>
       <c r="K648" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L648" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£210,000</t>
         </is>
       </c>
       <c r="N648" s="1" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="649">
@@ -35558,21 +35608,21 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>Accelerated Knowledge Transfer Partnerships 6 (AKT 6)</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2478/overview/77f0cc95-dd1b-450f-a02d-e83046b464c1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2473/overview/d9a164dd-2094-4590-baa7-a057279d80a3</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>2026-05-18 13:41</t>
+          <t>2026-05-16 10:59</t>
         </is>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46160.57013888889</v>
+        <v>46158.45763888889</v>
       </c>
       <c r="F649" t="b">
         <v>1</v>
@@ -35585,15 +35635,15 @@
       <c r="J649" t="inlineStr"/>
       <c r="K649" t="inlineStr">
         <is>
-          <t>Tuesday 1 September 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L649" s="1" t="n">
-        <v>46266.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N649" s="1" t="n">
@@ -35608,21 +35658,21 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>CfI Improving Outcomes for Children Experiencing Homelessness</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2460/overview/d840aec6-c35d-4d86-a524-2b4c5a9bf9b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2478/overview/77f0cc95-dd1b-450f-a02d-e83046b464c1</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>2026-05-19 12:36</t>
+          <t>2026-05-18 13:41</t>
         </is>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46161.525</v>
+        <v>46160.57013888889</v>
       </c>
       <c r="F650" t="b">
         <v>1</v>
@@ -35635,15 +35685,15 @@
       <c r="J650" t="inlineStr"/>
       <c r="K650" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Tuesday 1 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L650" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46266.45833333334</v>
       </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N650" s="1" t="n">
@@ -35658,21 +35708,21 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: industrial research (Research Organisations)</t>
+          <t>CfI Improving Outcomes for Children Experiencing Homelessness</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2497/overview/1abf98e8-4873-4fb7-b9d0-e702a2c9d80a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2460/overview/d840aec6-c35d-4d86-a524-2b4c5a9bf9b3</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>2026-05-28 13:43</t>
+          <t>2026-05-19 12:36</t>
         </is>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46170.57152777778</v>
+        <v>46161.525</v>
       </c>
       <c r="F651" t="b">
         <v>1</v>
@@ -35685,19 +35735,19 @@
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L651" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M651" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N651" s="1" t="n">
-        <v>46169</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="652">
@@ -35708,12 +35758,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C6</t>
+          <t>Future offshore wind technologies: industrial research (Research Organisations)</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2480/overview/96372f42-c714-4d17-91b0-dd75b9a80e17</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2497/overview/1abf98e8-4873-4fb7-b9d0-e702a2c9d80a</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -35735,15 +35785,15 @@
       <c r="J652" t="inlineStr"/>
       <c r="K652" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L652" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M652" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N652" s="1" t="n">
@@ -35758,12 +35808,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Discovery C6</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C6</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2484/overview/770c0946-2e24-4566-bab1-2bf1c1dd2b38</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2480/overview/96372f42-c714-4d17-91b0-dd75b9a80e17</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -35808,21 +35858,21 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 7 - Academic Partners</t>
+          <t>Ofgem Strategic Innovation Fund Discovery C6</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2500/overview/d7508935-cc7f-4971-8f0f-074f80317ed4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2484/overview/770c0946-2e24-4566-bab1-2bf1c1dd2b38</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>2026-05-29 12:45</t>
+          <t>2026-05-28 13:43</t>
         </is>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46171.53125</v>
+        <v>46170.57152777778</v>
       </c>
       <c r="F654" t="b">
         <v>1</v>
@@ -35835,15 +35885,15 @@
       <c r="J654" t="inlineStr"/>
       <c r="K654" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 24 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L654" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46197.45833333334</v>
       </c>
       <c r="M654" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N654" s="1" t="n">
@@ -35858,12 +35908,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 9</t>
+          <t>Full ADOPT Grant: Round 7 - Academic Partners</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2482/overview/a17ac084-56fa-4679-8d35-1f5602f27d29</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2500/overview/d7508935-cc7f-4971-8f0f-074f80317ed4</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -35885,15 +35935,15 @@
       <c r="J655" t="inlineStr"/>
       <c r="K655" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L655" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M655" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N655" s="1" t="n">
@@ -35908,21 +35958,21 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
+          <t>ADOPT Facilitator Support Grant: Round 9</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2482/overview/a17ac084-56fa-4679-8d35-1f5602f27d29</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>2026-06-03 14:24</t>
+          <t>2026-05-29 12:45</t>
         </is>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46176.6</v>
+        <v>46171.53125</v>
       </c>
       <c r="F656" t="b">
         <v>1</v>
@@ -35935,19 +35985,19 @@
       <c r="J656" t="inlineStr"/>
       <c r="K656" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L656" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M656" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N656" s="1" t="n">
-        <v>46176</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="657">
@@ -35958,12 +36008,12 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>ACTASAP Pilot Phase 1</t>
+          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2502/overview/35ca10fb-d4f5-4510-9ddd-e7e3133d2b6d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -35985,15 +36035,15 @@
       <c r="J657" t="inlineStr"/>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Tuesday 28 July 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L657" s="1" t="n">
-        <v>46231.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N657" s="1" t="n">
@@ -36008,12 +36058,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Scaling Supply Chains for Quantum Enabled Sensing and PNT</t>
+          <t>ACTASAP Pilot Phase 1</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2495/overview/b2a4cd81-a226-4a11-83c8-966284542f59</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2502/overview/35ca10fb-d4f5-4510-9ddd-e7e3133d2b6d</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -36035,15 +36085,15 @@
       <c r="J658" t="inlineStr"/>
       <c r="K658" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Tuesday 28 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L658" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46231.45833333334</v>
       </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N658" s="1" t="n">
@@ -36058,21 +36108,21 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 8</t>
+          <t>Scaling Supply Chains for Quantum Enabled Sensing and PNT</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2491/overview/77ba6cb6-c14d-41f7-84de-e45446636e50</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2495/overview/b2a4cd81-a226-4a11-83c8-966284542f59</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>2026-06-04 12:41</t>
+          <t>2026-06-03 14:24</t>
         </is>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46177.52847222222</v>
+        <v>46176.6</v>
       </c>
       <c r="F659" t="b">
         <v>1</v>
@@ -36085,15 +36135,15 @@
       <c r="J659" t="inlineStr"/>
       <c r="K659" t="inlineStr">
         <is>
-          <t>Wednesday 29 July 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L659" s="1" t="n">
-        <v>46232.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M659" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N659" s="1" t="n">
@@ -36108,21 +36158,21 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Innovation Loans Expression of Interest</t>
+          <t>Full ADOPT Grant: Round 8</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2491/overview/77ba6cb6-c14d-41f7-84de-e45446636e50</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2026-06-05 12:33</t>
+          <t>2026-06-04 12:41</t>
         </is>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46178.52291666667</v>
+        <v>46177.52847222222</v>
       </c>
       <c r="F660" t="b">
         <v>1</v>
@@ -36135,13 +36185,15 @@
       <c r="J660" t="inlineStr"/>
       <c r="K660" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L660" t="inlineStr"/>
+          <t>Wednesday 29 July 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L660" s="1" t="n">
+        <v>46232.45833333334</v>
+      </c>
       <c r="M660" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N660" s="1" t="n">
@@ -36156,21 +36208,21 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body summer 2026</t>
+          <t>Innovation Loans Expression of Interest</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2504/overview/05f2babb-c5b0-4b37-80dc-3883b41bc2c7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>2026-06-11 13:55</t>
+          <t>2026-06-05 12:33</t>
         </is>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46184.57986111111</v>
+        <v>46178.52291666667</v>
       </c>
       <c r="F661" t="b">
         <v>1</v>
@@ -36183,19 +36235,17 @@
       <c r="J661" t="inlineStr"/>
       <c r="K661" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L661" s="1" t="n">
-        <v>46211.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr"/>
       <c r="M661" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N661" s="1" t="n">
-        <v>46183</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="662">
@@ -36206,12 +36256,12 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Consumer Led Flexibility for the Clean Energy Superpower Mission</t>
+          <t>Robotics Adoption Central Convening Body summer 2026</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2509/overview/c1794f5a-06bf-41bb-8a13-3e657dacef54</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2504/overview/05f2babb-c5b0-4b37-80dc-3883b41bc2c7</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -36233,15 +36283,15 @@
       <c r="J662" t="inlineStr"/>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Wednesday 26 August 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L662" s="1" t="n">
-        <v>46260.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M662" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N662" s="1" t="n">
@@ -36256,21 +36306,21 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>UK-Switzerland CR&amp;D Round 3</t>
+          <t>Consumer Led Flexibility for the Clean Energy Superpower Mission</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2512/overview/2f0a03c4-44b7-42dc-8845-70751b6bc531</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2509/overview/c1794f5a-06bf-41bb-8a13-3e657dacef54</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2026-06-19 13:32</t>
+          <t>2026-06-11 13:55</t>
         </is>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46192.56388888889</v>
+        <v>46184.57986111111</v>
       </c>
       <c r="F663" t="b">
         <v>1</v>
@@ -36283,19 +36333,19 @@
       <c r="J663" t="inlineStr"/>
       <c r="K663" t="inlineStr">
         <is>
-          <t>Thursday 3 September 2026 11:00am</t>
+          <t>Wednesday 26 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L663" s="1" t="n">
-        <v>46268.45833333334</v>
+        <v>46260.45833333334</v>
       </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>£450,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N663" s="1" t="n">
-        <v>46190</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="664">
@@ -36306,21 +36356,21 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>CfI: Earlier identification of UK children with SEN</t>
+          <t>UK-Switzerland CR&amp;D Round 3</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2511/overview/cc9f4bb9-55a5-4b4c-9843-015c385e021f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2512/overview/2f0a03c4-44b7-42dc-8845-70751b6bc531</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>2026-06-22 15:20</t>
+          <t>2026-06-19 13:32</t>
         </is>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46195.63888888889</v>
+        <v>46192.56388888889</v>
       </c>
       <c r="F664" t="b">
         <v>1</v>
@@ -36333,15 +36383,15 @@
       <c r="J664" t="inlineStr"/>
       <c r="K664" t="inlineStr">
         <is>
-          <t>Wednesday 5 August 2026 11:00am</t>
+          <t>Thursday 3 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L664" s="1" t="n">
-        <v>46239.45833333334</v>
+        <v>46268.45833333334</v>
       </c>
       <c r="M664" t="inlineStr">
         <is>
-          <t>£500</t>
+          <t>£450,000</t>
         </is>
       </c>
       <c r="N664" s="1" t="n">
@@ -36356,12 +36406,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>DRIVE35: Scale Up Fund</t>
+          <t>CfI: Earlier identification of UK children with SEN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2445/overview/a850ba04-f0b3-42c5-8dfa-03375731a884</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2511/overview/cc9f4bb9-55a5-4b4c-9843-015c385e021f</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -36383,13 +36433,15 @@
       <c r="J665" t="inlineStr"/>
       <c r="K665" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L665" t="inlineStr"/>
+          <t>Wednesday 5 August 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L665" s="1" t="n">
+        <v>46239.45833333334</v>
+      </c>
       <c r="M665" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£500</t>
         </is>
       </c>
       <c r="N665" s="1" t="n">
@@ -36404,21 +36456,21 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Next Wave: Breakthrough Wave 1</t>
+          <t>DRIVE35: Scale Up Fund</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2517/overview/6ff2066d-4639-44e6-bb4f-ce7099222739</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2445/overview/a850ba04-f0b3-42c5-8dfa-03375731a884</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>2026-06-23 12:29</t>
+          <t>2026-06-22 15:20</t>
         </is>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46196.52013888889</v>
+        <v>46195.63888888889</v>
       </c>
       <c r="F666" t="b">
         <v>1</v>
@@ -36431,15 +36483,13 @@
       <c r="J666" t="inlineStr"/>
       <c r="K666" t="inlineStr">
         <is>
-          <t>Tuesday 11 August 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L666" s="1" t="n">
-        <v>46245.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr"/>
       <c r="M666" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N666" s="1" t="n">
@@ -36454,21 +36504,21 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
+          <t>Next Wave: Breakthrough Wave 1</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2517/overview/6ff2066d-4639-44e6-bb4f-ce7099222739</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>2026-06-26 12:08</t>
+          <t>2026-06-23 12:29</t>
         </is>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46199.50555555556</v>
+        <v>46196.52013888889</v>
       </c>
       <c r="F667" t="b">
         <v>1</v>
@@ -36481,19 +36531,19 @@
       <c r="J667" t="inlineStr"/>
       <c r="K667" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Tuesday 11 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L667" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46245.45833333334</v>
       </c>
       <c r="M667" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N667" s="1" t="n">
-        <v>46197</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="668">
@@ -36504,21 +36554,21 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>2026-06-27 11:24</t>
+          <t>2026-06-26 12:08</t>
         </is>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46200.475</v>
+        <v>46199.50555555556</v>
       </c>
       <c r="F668" t="b">
         <v>1</v>
@@ -36531,15 +36581,15 @@
       <c r="J668" t="inlineStr"/>
       <c r="K668" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L668" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N668" s="1" t="n">
@@ -36554,21 +36604,21 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 10</t>
+          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2520/overview/7b03dc59-645f-426d-a08f-6c6e6b6d6e0e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>2026-07-10 12:22</t>
+          <t>2026-06-27 11:24</t>
         </is>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46213.51527777778</v>
+        <v>46200.475</v>
       </c>
       <c r="F669" t="b">
         <v>1</v>
@@ -36581,19 +36631,19 @@
       <c r="J669" t="inlineStr"/>
       <c r="K669" t="inlineStr">
         <is>
-          <t>Wednesday 12 August 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L669" s="1" t="n">
-        <v>46246.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N669" s="1" t="n">
-        <v>46211</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="670">
@@ -36604,21 +36654,21 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 5</t>
+          <t>ADOPT Facilitator Support Grant: Round 10</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2529/overview/7a278b3b-4e22-4702-a8aa-7491d9a11e36</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2520/overview/7b03dc59-645f-426d-a08f-6c6e6b6d6e0e</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>2026-07-15 11:25</t>
+          <t>2026-07-10 12:22</t>
         </is>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46218.47569444445</v>
+        <v>46213.51527777778</v>
       </c>
       <c r="F670" t="b">
         <v>1</v>
@@ -36631,19 +36681,19 @@
       <c r="J670" t="inlineStr"/>
       <c r="K670" t="inlineStr">
         <is>
-          <t>Wednesday 9 September 2026 11:00am</t>
+          <t>Wednesday 12 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L670" s="1" t="n">
-        <v>46274.45833333334</v>
+        <v>46246.45833333334</v>
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N670" s="1" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="671">
@@ -36654,21 +36704,21 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Advanced Connectivity Technologies: New Innovators</t>
+          <t>Farming Innovation Programme: Feasibility Round 5</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2513/overview/cbe58d4f-05a7-4eca-976b-e2de751b47ae</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2529/overview/7a278b3b-4e22-4702-a8aa-7491d9a11e36</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>2026-07-17 11:18</t>
+          <t>2026-07-15 11:25</t>
         </is>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46220.47083333333</v>
+        <v>46218.47569444445</v>
       </c>
       <c r="F671" t="b">
         <v>1</v>
@@ -36681,15 +36731,15 @@
       <c r="J671" t="inlineStr"/>
       <c r="K671" t="inlineStr">
         <is>
-          <t>Wednesday 5 August 2026 11:00am</t>
+          <t>Wednesday 9 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L671" s="1" t="n">
-        <v>46239.45833333334</v>
+        <v>46274.45833333334</v>
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N671" s="1" t="n">
@@ -36704,21 +36754,21 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Ultra Long Duration Energy Storage Project Development Studies</t>
+          <t>Advanced Connectivity Technologies: New Innovators</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2531/overview/5f2a43fb-9581-4892-8e15-86c2c0c814cd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2513/overview/cbe58d4f-05a7-4eca-976b-e2de751b47ae</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>2026-08-03 12:52</t>
+          <t>2026-07-17 11:18</t>
         </is>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46237.53611111111</v>
+        <v>46220.47083333333</v>
       </c>
       <c r="F672" t="b">
         <v>1</v>
@@ -36731,19 +36781,19 @@
       <c r="J672" t="inlineStr"/>
       <c r="K672" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 5 August 2026 11:00am</t>
         </is>
       </c>
       <c r="L672" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46239.45833333334</v>
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>£700,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N672" s="1" t="n">
-        <v>46232</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="673">
@@ -36754,12 +36804,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
+          <t>Ultra Long Duration Energy Storage Project Development Studies</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2531/overview/5f2a43fb-9581-4892-8e15-86c2c0c814cd</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -36789,7 +36839,7 @@
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£700,000</t>
         </is>
       </c>
       <c r="N673" s="1" t="n">
@@ -36804,21 +36854,21 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
+          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-03 12:52</t>
         </is>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46238.49930555555</v>
+        <v>46237.53611111111</v>
       </c>
       <c r="F674" t="b">
         <v>1</v>
@@ -36831,15 +36881,15 @@
       <c r="J674" t="inlineStr"/>
       <c r="K674" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L674" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M674" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N674" s="1" t="n">
@@ -36854,12 +36904,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
+          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -36889,7 +36939,7 @@
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N675" s="1" t="n">
@@ -36904,21 +36954,21 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
+          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>2026-08-10 11:02</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46244.45972222222</v>
+        <v>46238.49930555555</v>
       </c>
       <c r="F676" t="b">
         <v>1</v>
@@ -36931,19 +36981,19 @@
       <c r="J676" t="inlineStr"/>
       <c r="K676" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L676" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N676" s="1" t="n">
-        <v>46239</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="677">
@@ -36954,21 +37004,21 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>UK-Singapore CRD 2026</t>
+          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>2026-08-13 10:57</t>
+          <t>2026-08-10 11:02</t>
         </is>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46247.45625</v>
+        <v>46244.45972222222</v>
       </c>
       <c r="F677" t="b">
         <v>1</v>
@@ -36981,19 +37031,19 @@
       <c r="J677" t="inlineStr"/>
       <c r="K677" t="inlineStr">
         <is>
-          <t>Wednesday 16 December 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L677" s="1" t="n">
-        <v>46372.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>£900,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N677" s="1" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="678">
@@ -37004,21 +37054,21 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 9</t>
+          <t>UK-Singapore CRD 2026</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>2026-08-14 10:53</t>
+          <t>2026-08-13 10:57</t>
         </is>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46248.45347222222</v>
+        <v>46247.45625</v>
       </c>
       <c r="F678" t="b">
         <v>1</v>
@@ -37031,15 +37081,15 @@
       <c r="J678" t="inlineStr"/>
       <c r="K678" t="inlineStr">
         <is>
-          <t>Wednesday 23 September 2026 11:00am</t>
+          <t>Wednesday 16 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L678" s="1" t="n">
-        <v>46288.45833333334</v>
+        <v>46372.45833333334</v>
       </c>
       <c r="M678" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£900,000</t>
         </is>
       </c>
       <c r="N678" s="1" t="n">
@@ -37054,12 +37104,12 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
+          <t>Full ADOPT Grant: Round 9</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -37081,13 +37131,17 @@
       <c r="J679" t="inlineStr"/>
       <c r="K679" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 23 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L679" s="1" t="n">
-        <v>46309.45833333334</v>
-      </c>
-      <c r="M679" t="inlineStr"/>
+        <v>46288.45833333334</v>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>£200,000</t>
+        </is>
+      </c>
       <c r="N679" s="1" t="n">
         <v>46246</v>
       </c>
@@ -37100,21 +37154,21 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Advancing innovation in accelerated cancer diagnosis</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>2026-08-19 10:22</t>
+          <t>2026-08-14 10:53</t>
         </is>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46253.43194444444</v>
+        <v>46248.45347222222</v>
       </c>
       <c r="F680" t="b">
         <v>1</v>
@@ -37127,19 +37181,15 @@
       <c r="J680" t="inlineStr"/>
       <c r="K680" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L680" s="1" t="n">
-        <v>46323.45833333334</v>
-      </c>
-      <c r="M680" t="inlineStr">
-        <is>
-          <t>£4.0 million</t>
-        </is>
-      </c>
+        <v>46309.45833333334</v>
+      </c>
+      <c r="M680" t="inlineStr"/>
       <c r="N680" s="1" t="n">
-        <v>46253</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="681">
@@ -37150,21 +37200,21 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 11</t>
+          <t>Advancing innovation in accelerated cancer diagnosis</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2026-08-20 10:23</t>
+          <t>2026-08-19 10:22</t>
         </is>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46254.43263888889</v>
+        <v>46253.43194444444</v>
       </c>
       <c r="F681" t="b">
         <v>1</v>
@@ -37177,15 +37227,15 @@
       <c r="J681" t="inlineStr"/>
       <c r="K681" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L681" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M681" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N681" s="1" t="n">
@@ -37200,21 +37250,21 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
+          <t>ADOPT Facilitator Support Grant: Round 11</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17</t>
+          <t>2026-08-20 10:23</t>
         </is>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46256.42847222222</v>
+        <v>46254.43263888889</v>
       </c>
       <c r="F682" t="b">
         <v>1</v>
@@ -37227,15 +37277,15 @@
       <c r="J682" t="inlineStr"/>
       <c r="K682" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L682" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M682" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N682" s="1" t="n">
@@ -37250,21 +37300,21 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
+          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2026-08-26 10:29</t>
+          <t>2026-08-22 10:17</t>
         </is>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46260.43680555555</v>
+        <v>46256.42847222222</v>
       </c>
       <c r="F683" t="b">
         <v>1</v>
@@ -37277,19 +37327,19 @@
       <c r="J683" t="inlineStr"/>
       <c r="K683" t="inlineStr">
         <is>
-          <t>Wednesday 7 October 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L683" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>£80,420</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N683" s="1" t="n">
-        <v>46260</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="684">
@@ -37300,21 +37350,21 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
+          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>2026-08-28 21:03</t>
+          <t>2026-08-26 10:29</t>
         </is>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46262.87708333333</v>
+        <v>46260.43680555555</v>
       </c>
       <c r="F684" t="b">
         <v>1</v>
@@ -37327,15 +37377,15 @@
       <c r="J684" t="inlineStr"/>
       <c r="K684" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 7 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L684" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£80,420</t>
         </is>
       </c>
       <c r="N684" s="1" t="n">
@@ -37350,12 +37400,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Investor Partnerships – ACT and Semiconductors</t>
+          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -37377,15 +37427,15 @@
       <c r="J685" t="inlineStr"/>
       <c r="K685" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L685" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N685" s="1" t="n">
@@ -37400,21 +37450,21 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
+          <t>Investor Partnerships – ACT and Semiconductors</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>2026-09-01 14:28</t>
+          <t>2026-08-28 21:03</t>
         </is>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46266.60277777778</v>
+        <v>46262.87708333333</v>
       </c>
       <c r="F686" t="b">
         <v>1</v>
@@ -37435,7 +37485,7 @@
       </c>
       <c r="M686" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N686" s="1" t="n">
@@ -37450,12 +37500,12 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -37485,7 +37535,7 @@
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N687" s="1" t="n">
@@ -37500,21 +37550,21 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing Data Institute: Phase 1</t>
+          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-01 14:28</t>
         </is>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46269.58055555556</v>
+        <v>46266.60277777778</v>
       </c>
       <c r="F688" t="b">
         <v>1</v>
@@ -37535,11 +37585,11 @@
       </c>
       <c r="M688" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N688" s="1" t="n">
-        <v>46267</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="689">
@@ -37550,21 +37600,21 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
+          <t>Medicines Manufacturing Data Institute: Phase 1</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46272.64375</v>
+        <v>46269.58055555556</v>
       </c>
       <c r="F689" t="b">
         <v>1</v>
@@ -37577,15 +37627,15 @@
       <c r="J689" t="inlineStr"/>
       <c r="K689" t="inlineStr">
         <is>
-          <t>Tuesday 3 November 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L689" s="1" t="n">
-        <v>46329.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N689" s="1" t="n">
@@ -37600,12 +37650,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Engineering Biology Access to Infrastructure Pilot</t>
+          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -37627,15 +37677,15 @@
       <c r="J690" t="inlineStr"/>
       <c r="K690" t="inlineStr">
         <is>
-          <t>Wednesday 21 October 2026 11:00am</t>
+          <t>Tuesday 3 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L690" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46329.45833333334</v>
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N690" s="1" t="n">
@@ -37650,21 +37700,21 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
+          <t>Engineering Biology Access to Infrastructure Pilot</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-07 15:27</t>
         </is>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46276.58333333334</v>
+        <v>46272.64375</v>
       </c>
       <c r="F691" t="b">
         <v>1</v>
@@ -37677,19 +37727,19 @@
       <c r="J691" t="inlineStr"/>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 21 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L691" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>£700,000</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N691" s="1" t="n">
-        <v>46274</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="692">
@@ -37700,12 +37750,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Battery Innovation: Feasibility Studies Rd 3</t>
+          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -37727,15 +37777,15 @@
       <c r="J692" t="inlineStr"/>
       <c r="K692" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L692" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£700,000</t>
         </is>
       </c>
       <c r="N692" s="1" t="n">
@@ -37750,12 +37800,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Battery Innovation: Concept Development Rd 3</t>
+          <t>Battery Innovation: Feasibility Studies Rd 3</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -37785,7 +37835,7 @@
       </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N693" s="1" t="n">
@@ -37800,21 +37850,21 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>CfI: Innovation in play to improve child outcomes</t>
+          <t>Battery Innovation: Concept Development Rd 3</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2573/overview/0260e1f5-c985-4858-aee3-57a9e56f19fe</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>2026-09-15 14:35</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46280.60763888889</v>
+        <v>46276.58333333334</v>
       </c>
       <c r="F694" t="b">
         <v>1</v>
@@ -37827,15 +37877,15 @@
       <c r="J694" t="inlineStr"/>
       <c r="K694" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L694" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N694" s="1" t="n">
@@ -37860,11 +37910,11 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36</t>
+          <t>2026-09-15 14:35</t>
         </is>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46282.60833333333</v>
+        <v>46280.60763888889</v>
       </c>
       <c r="F695" t="b">
         <v>1</v>
@@ -37889,7 +37939,7 @@
         </is>
       </c>
       <c r="N695" s="1" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="696">
@@ -37900,12 +37950,12 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
+          <t>CfI: Innovation in play to improve child outcomes</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2573/overview/0260e1f5-c985-4858-aee3-57a9e56f19fe</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -37927,15 +37977,15 @@
       <c r="J696" t="inlineStr"/>
       <c r="K696" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L696" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>£700,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N696" s="1" t="n">
@@ -37950,12 +38000,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Battery Innovation: Feasibility Studies Rd 3</t>
+          <t>Ultra Long Duration Energy Storage Project Development Studies Relaunch</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2574/overview/48cb1c09-fcef-4ae8-a700-d79db606fba8</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -37977,15 +38027,15 @@
       <c r="J697" t="inlineStr"/>
       <c r="K697" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L697" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£700,000</t>
         </is>
       </c>
       <c r="N697" s="1" t="n">
@@ -38000,12 +38050,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Battery Innovation: Concept Development Rd 3</t>
+          <t>Battery Innovation: Feasibility Studies Rd 3</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2571/overview/f45e5f00-e663-4c9e-a2e7-562a696561d7</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -38035,7 +38085,7 @@
       </c>
       <c r="M698" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N698" s="1" t="n">
@@ -38050,12 +38100,12 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
+          <t>Battery Innovation: Concept Development Rd 3</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2572/overview/7410b013-814e-4db6-9011-c39efe67e2d6</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -38077,15 +38127,15 @@
       <c r="J699" t="inlineStr"/>
       <c r="K699" t="inlineStr">
         <is>
-          <t>Tuesday 3 November 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L699" s="1" t="n">
-        <v>46329.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N699" s="1" t="n">
@@ -38100,12 +38150,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing Data Institute: Phase 1</t>
+          <t>Engineering Biology Collaborative R&amp;D: Round 3</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2542/overview/b687b240-4dff-4149-889b-308e61447460</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -38127,15 +38177,15 @@
       <c r="J700" t="inlineStr"/>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Tuesday 3 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L700" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46329.45833333334</v>
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N700" s="1" t="n">
@@ -38150,12 +38200,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Engineering Biology Access to Infrastructure Pilot</t>
+          <t>Medicines Manufacturing Data Institute: Phase 1</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2533/overview/60eae26d-934b-413d-9f63-4ad575c13dc3</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -38177,15 +38227,15 @@
       <c r="J701" t="inlineStr"/>
       <c r="K701" t="inlineStr">
         <is>
-          <t>Wednesday 21 October 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L701" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N701" s="1" t="n">
@@ -38200,12 +38250,12 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
+          <t>Engineering Biology Access to Infrastructure Pilot</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2546/overview/d8b3252c-a147-4088-89ab-7991141da64a</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -38227,15 +38277,15 @@
       <c r="J702" t="inlineStr"/>
       <c r="K702" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 21 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L702" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N702" s="1" t="n">
@@ -38250,12 +38300,12 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Investor Partnerships – ACT and Semiconductors</t>
+          <t>National Materials Innovation Programme: CR&amp;D Rd1</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2569/overview/a3448c9e-38ae-4759-957c-bccf6c40c281</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -38277,15 +38327,15 @@
       <c r="J703" t="inlineStr"/>
       <c r="K703" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L703" s="1" t="n">
-        <v>46309.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N703" s="1" t="n">
@@ -38300,12 +38350,12 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
+          <t>Investor Partnerships – ACT and Semiconductors</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2567/overview/53ee8d14-5670-4f09-8825-0d7ca9c09100</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -38335,7 +38385,7 @@
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N704" s="1" t="n">
@@ -38350,12 +38400,12 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 5</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2568/overview/b30aae16-96ab-45c1-9e27-11ebf9d41969</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -38385,7 +38435,7 @@
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N705" s="1" t="n">
@@ -38400,12 +38450,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Advancing innovation in accelerated cancer diagnosis</t>
+          <t>CfI: Engineering Biology for Defra and FSA Phase 1</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2566/overview/bd333690-b6c6-4bdc-8447-4c8b5853ef52</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -38427,15 +38477,15 @@
       <c r="J706" t="inlineStr"/>
       <c r="K706" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L706" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N706" s="1" t="n">
@@ -38450,12 +38500,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
+          <t>Advancing innovation in accelerated cancer diagnosis</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2527/overview/d48f61f8-2bd5-4067-9c05-29dd08487623</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -38477,15 +38527,15 @@
       <c r="J707" t="inlineStr"/>
       <c r="K707" t="inlineStr">
         <is>
-          <t>Wednesday 7 October 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L707" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>£80,420</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N707" s="1" t="n">
@@ -38500,12 +38550,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>UK-Singapore CRD 2026</t>
+          <t>Advanced Manufacturing: Measurement and Sensing Pilot</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2559/overview/54e68d9c-8be2-449c-8b6b-07fcd5014582</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -38527,15 +38577,15 @@
       <c r="J708" t="inlineStr"/>
       <c r="K708" t="inlineStr">
         <is>
-          <t>Wednesday 16 December 2026 11:00am</t>
+          <t>Wednesday 7 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L708" s="1" t="n">
-        <v>46372.45833333334</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>£900,000</t>
+          <t>£80,420</t>
         </is>
       </c>
       <c r="N708" s="1" t="n">
@@ -38550,12 +38600,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
+          <t>UK-Singapore CRD 2026</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2526/overview/4a4b67b9-9b73-4816-8e21-bdfab83f5909</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -38577,15 +38627,15 @@
       <c r="J709" t="inlineStr"/>
       <c r="K709" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Wednesday 16 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L709" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46372.45833333334</v>
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£900,000</t>
         </is>
       </c>
       <c r="N709" s="1" t="n">
@@ -38600,12 +38650,12 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 11</t>
+          <t>Electricity Demand Turn Up trial: EOI for flexibility providers</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2557/overview/07ff6bbf-0eaf-4798-9fb3-5f2004211893</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -38627,15 +38677,15 @@
       <c r="J710" t="inlineStr"/>
       <c r="K710" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L710" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N710" s="1" t="n">
@@ -38650,12 +38700,12 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 9</t>
+          <t>ADOPT Facilitator Support Grant: Round 11</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2556/overview/ff6d6e0a-92ee-4719-a0fb-2e4bc2aa9c4d</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -38677,15 +38727,15 @@
       <c r="J711" t="inlineStr"/>
       <c r="K711" t="inlineStr">
         <is>
-          <t>Wednesday 7 October 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L711" s="1" t="n">
-        <v>46302.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M711" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N711" s="1" t="n">
@@ -38700,12 +38750,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
+          <t>Full ADOPT Grant: Round 9</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2544/overview/fe16ecd4-5413-4fa5-8ccc-4bfdcb390944</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -38727,13 +38777,17 @@
       <c r="J712" t="inlineStr"/>
       <c r="K712" t="inlineStr">
         <is>
-          <t>Wednesday 14 October 2026 11:00am</t>
+          <t>Wednesday 7 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L712" s="1" t="n">
-        <v>46309.45833333334</v>
-      </c>
-      <c r="M712" t="inlineStr"/>
+        <v>46302.45833333334</v>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>£200,000</t>
+        </is>
+      </c>
       <c r="N712" s="1" t="n">
         <v>46281</v>
       </c>
@@ -38746,12 +38800,12 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 3</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2514/overview/81b3dcb8-7d03-42ed-8b97-5e6e51c4d1ed</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -38773,17 +38827,13 @@
       <c r="J713" t="inlineStr"/>
       <c r="K713" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Wednesday 14 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L713" s="1" t="n">
-        <v>46330.45833333334</v>
-      </c>
-      <c r="M713" t="inlineStr">
-        <is>
-          <t>£20.0 million</t>
-        </is>
-      </c>
+        <v>46309.45833333334</v>
+      </c>
+      <c r="M713" t="inlineStr"/>
       <c r="N713" s="1" t="n">
         <v>46281</v>
       </c>
@@ -38796,12 +38846,12 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
+          <t>DRIVE35 Scale-up Fund Drawdown 5</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2541/overview/9b9c9265-c1dd-490a-ac00-18a98642350a</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -38823,15 +38873,15 @@
       <c r="J714" t="inlineStr"/>
       <c r="K714" t="inlineStr">
         <is>
-          <t>Thursday 24 September 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L714" s="1" t="n">
-        <v>46289.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N714" s="1" t="n">
@@ -38846,12 +38896,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
+          <t>Quantum computing applications for large scale impact: CR&amp;D</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2525/overview/b1c3d8b5-575f-47c8-952d-22fc766fe802</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -38873,15 +38923,15 @@
       <c r="J715" t="inlineStr"/>
       <c r="K715" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Thursday 24 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L715" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46289.45833333334</v>
       </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N715" s="1" t="n">
@@ -38896,12 +38946,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
+          <t>Accelerating adoption of quantum enabled sensing and PNT</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2539/overview/d3ba2c8c-c752-4d49-90d6-e0a56f232c3c</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -38923,15 +38973,15 @@
       <c r="J716" t="inlineStr"/>
       <c r="K716" t="inlineStr">
         <is>
-          <t>Wednesday 30 September 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L716" s="1" t="n">
-        <v>46295.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N716" s="1" t="n">
@@ -38946,12 +38996,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
+          <t>Farming Futures R&amp;D fund: Automation and Robotics Round 2</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2536/overview/2999eaf5-b86c-466d-88c0-00b362a50ac8</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -38973,15 +39023,15 @@
       <c r="J717" t="inlineStr"/>
       <c r="K717" t="inlineStr">
         <is>
-          <t>Friday 2 October 2026 11:00am</t>
+          <t>Wednesday 30 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L717" s="1" t="n">
-        <v>46297.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="M717" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N717" s="1" t="n">
@@ -38996,12 +39046,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
+          <t>Scaling performance of quantum computing hardware: CR&amp;D</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2523/overview/780f14e7-b64d-4264-b206-b498304d03c5</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -39023,15 +39073,15 @@
       <c r="J718" t="inlineStr"/>
       <c r="K718" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
+          <t>Friday 2 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L718" s="1" t="n">
-        <v>46283.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="M718" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N718" s="1" t="n">
@@ -39046,12 +39096,12 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 3</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2522/overview/25a1cadb-ab0d-4d6d-a629-4f5d3ead5994</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -39073,15 +39123,15 @@
       <c r="J719" t="inlineStr"/>
       <c r="K719" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L719" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N719" s="1" t="n">
@@ -39096,12 +39146,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Innovation Loans Expression of Interest</t>
+          <t>Future Leaders Fellowships: Round 11, business and non-academic</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2499/overview/60da9000-d438-47fb-92aa-e8d9435a17ab</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -39123,13 +39173,15 @@
       <c r="J720" t="inlineStr"/>
       <c r="K720" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L720" t="inlineStr"/>
+          <t>Wednesday 4 November 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L720" s="1" t="n">
+        <v>46330.45833333334</v>
+      </c>
       <c r="M720" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N720" s="1" t="n">
@@ -39144,12 +39196,12 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
+          <t>Innovation Loans Expression of Interest</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2505/overview/8ef63f10-ea07-4ffd-9812-e944542751b6</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -39171,15 +39223,13 @@
       <c r="J721" t="inlineStr"/>
       <c r="K721" t="inlineStr">
         <is>
-          <t>Friday 18 September 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L721" s="1" t="n">
-        <v>46283.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr"/>
       <c r="M721" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N721" s="1" t="n">
@@ -39194,12 +39244,12 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -39244,12 +39294,12 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -39294,21 +39344,21 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C7</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2550/overview/5cbb2d13-74bb-41b1-be19-005376930f80</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>2026-09-18 14:02</t>
+          <t>2026-09-17 14:36</t>
         </is>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46283.58472222222</v>
+        <v>46282.60833333333</v>
       </c>
       <c r="F724" t="b">
         <v>1</v>
@@ -39321,15 +39371,15 @@
       <c r="J724" t="inlineStr"/>
       <c r="K724" t="inlineStr">
         <is>
-          <t>Wednesday 21 October 2026 11:00am</t>
+          <t>Friday 18 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L724" s="1" t="n">
-        <v>46316.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N724" s="1" t="n">
@@ -39344,12 +39394,12 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Discovery C7</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C7</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2552/overview/9f47273b-291d-4328-a49e-a038eff65f0d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2550/overview/5cbb2d13-74bb-41b1-be19-005376930f80</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -39394,21 +39444,21 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>Ofgem Strategic Innovation Fund Discovery C7</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2579/overview/3eaba59f-330d-45f6-a406-78067a71bb70</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2552/overview/9f47273b-291d-4328-a49e-a038eff65f0d</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>2026-09-19 13:39</t>
+          <t>2026-09-18 14:02</t>
         </is>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284.56875</v>
+        <v>46283.58472222222</v>
       </c>
       <c r="F726" t="b">
         <v>1</v>
@@ -39421,15 +39471,15 @@
       <c r="J726" t="inlineStr"/>
       <c r="K726" t="inlineStr">
         <is>
-          <t>Tuesday 1 December 2026 11:00am</t>
+          <t>Wednesday 21 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L726" s="1" t="n">
-        <v>46357.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N726" s="1" t="n">
@@ -39444,21 +39494,21 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>CfI: Counter UAS Demonstrations in Prison Environments</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2570/overview/f33d0d62-4658-43fd-ae3d-b6362ebff0f0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2579/overview/3eaba59f-330d-45f6-a406-78067a71bb70</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>2026-09-24 14:35</t>
+          <t>2026-09-19 13:39</t>
         </is>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46289.60763888889</v>
+        <v>46284.56875</v>
       </c>
       <c r="F727" t="b">
         <v>1</v>
@@ -39471,19 +39521,19 @@
       <c r="J727" t="inlineStr"/>
       <c r="K727" t="inlineStr">
         <is>
-          <t>Wednesday 28 October 2026 11:00am</t>
+          <t>Tuesday 1 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L727" s="1" t="n">
-        <v>46323.45833333334</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="M727" t="inlineStr">
         <is>
-          <t>£80,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N727" s="1" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="728">
@@ -39494,12 +39544,12 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Frontier AI: SME Champions, Phase 1</t>
+          <t>CfI: Counter UAS Demonstrations in Prison Environments</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2584/overview/4c7afb5d-4572-4ef2-9507-73ef2dec8ec8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2570/overview/f33d0d62-4658-43fd-ae3d-b6362ebff0f0</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -39521,15 +39571,15 @@
       <c r="J728" t="inlineStr"/>
       <c r="K728" t="inlineStr">
         <is>
-          <t>Wednesday 11 November 2026 11:00am</t>
+          <t>Wednesday 28 October 2026 11:00am</t>
         </is>
       </c>
       <c r="L728" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46323.45833333334</v>
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£80,000</t>
         </is>
       </c>
       <c r="N728" s="1" t="n">
@@ -39544,21 +39594,21 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Efficient, Structured and Controllable AI Systems</t>
+          <t>Frontier AI: SME Champions, Phase 1</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2582/overview/9fdb47a5-011c-4c47-ac5e-c426e295fe89</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2584/overview/4c7afb5d-4572-4ef2-9507-73ef2dec8ec8</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>2026-09-25 14:56</t>
+          <t>2026-09-24 14:35</t>
         </is>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46290.62222222222</v>
+        <v>46289.60763888889</v>
       </c>
       <c r="F729" t="b">
         <v>1</v>
@@ -39571,15 +39621,15 @@
       <c r="J729" t="inlineStr"/>
       <c r="K729" t="inlineStr">
         <is>
-          <t>Wednesday 18 November 2026 11:00am</t>
+          <t>Wednesday 11 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L729" s="1" t="n">
-        <v>46344.45833333334</v>
+        <v>46337.45833333334</v>
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N729" s="1" t="n">
@@ -39594,21 +39644,21 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>UK-Germany Bilateral Collaborative R&amp;D: Round 5</t>
+          <t>Efficient, Structured and Controllable AI Systems</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2583/overview/852abf67-ada4-49d3-b512-cf7c5ec6ac71</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2582/overview/9fdb47a5-011c-4c47-ac5e-c426e295fe89</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-25 14:56</t>
         </is>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46293.74652777778</v>
+        <v>46290.62222222222</v>
       </c>
       <c r="F730" t="b">
         <v>1</v>
@@ -39621,15 +39671,15 @@
       <c r="J730" t="inlineStr"/>
       <c r="K730" t="inlineStr">
         <is>
-          <t>Tuesday 1 December 2026 11:00am</t>
+          <t>Wednesday 18 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L730" s="1" t="n">
-        <v>46357.45833333334</v>
+        <v>46344.45833333334</v>
       </c>
       <c r="M730" t="inlineStr">
         <is>
-          <t>£350,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N730" s="1" t="n">
@@ -39644,21 +39694,21 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>CfI: Battery innovation for dual use &amp; defence Phase 1</t>
+          <t>UK-Germany Bilateral Collaborative R&amp;D: Round 5</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2587/overview/aafc825c-421e-47ea-bd56-d5d1cd50e513</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2583/overview/852abf67-ada4-49d3-b512-cf7c5ec6ac71</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2026-09-29 16:18</t>
+          <t>2026-09-28 17:55</t>
         </is>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46294.67916666667</v>
+        <v>46293.74652777778</v>
       </c>
       <c r="F731" t="b">
         <v>1</v>
@@ -39671,15 +39721,15 @@
       <c r="J731" t="inlineStr"/>
       <c r="K731" t="inlineStr">
         <is>
-          <t>Wednesday 4 November 2026 11:00am</t>
+          <t>Tuesday 1 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L731" s="1" t="n">
-        <v>46330.45833333334</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="M731" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£350,000</t>
         </is>
       </c>
       <c r="N731" s="1" t="n">
@@ -39694,21 +39744,21 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Engineering Biology Investor Partnerships Round 1</t>
+          <t>CfI: Battery innovation for dual use &amp; defence Phase 1</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2580/overview/8881af18-31f4-4db3-9483-cbb047163164</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2587/overview/aafc825c-421e-47ea-bd56-d5d1cd50e513</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>2026-10-01 16:50</t>
+          <t>2026-09-29 16:18</t>
         </is>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46296.70138888889</v>
+        <v>46294.67916666667</v>
       </c>
       <c r="F732" t="b">
         <v>1</v>
@@ -39721,19 +39771,19 @@
       <c r="J732" t="inlineStr"/>
       <c r="K732" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 4 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L732" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46330.45833333334</v>
       </c>
       <c r="M732" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N732" s="1" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="733">
@@ -39744,21 +39794,21 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>MDI Programme Innovation and Scale-up Hub</t>
+          <t>Engineering Biology Investor Partnerships Round 1</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2588/overview/acbd9666-c1df-4635-b86f-fa426100c876</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2580/overview/8881af18-31f4-4db3-9483-cbb047163164</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>2026-10-03 14:31</t>
+          <t>2026-10-01 16:50</t>
         </is>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298.60486111111</v>
+        <v>46296.70138888889</v>
       </c>
       <c r="F733" t="b">
         <v>1</v>
@@ -39771,15 +39821,15 @@
       <c r="J733" t="inlineStr"/>
       <c r="K733" t="inlineStr">
         <is>
-          <t>Wednesday 18 November 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L733" s="1" t="n">
-        <v>46344.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M733" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N733" s="1" t="n">
@@ -39794,21 +39844,21 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Eureka collaborative R&amp;D: Globalstars Japan 2027</t>
+          <t>MDI Programme Innovation and Scale-up Hub</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2586/overview/d9e61ae4-6e56-4f38-9206-5d91ef98c916</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2588/overview/acbd9666-c1df-4635-b86f-fa426100c876</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>2026-10-05 19:06</t>
+          <t>2026-10-03 14:31</t>
         </is>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46300.79583333333</v>
+        <v>46298.60486111111</v>
       </c>
       <c r="F734" t="b">
         <v>1</v>
@@ -39821,15 +39871,15 @@
       <c r="J734" t="inlineStr"/>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Wednesday 20 January 2027 11:00am</t>
+          <t>Wednesday 18 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L734" s="1" t="n">
-        <v>46407.45833333334</v>
+        <v>46344.45833333334</v>
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N734" s="1" t="n">
@@ -39844,12 +39894,12 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Sustainable Medicines Manufacturing Innovation: CR&amp;D Round 2</t>
+          <t>Eureka collaborative R&amp;D: Globalstars Japan 2027</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2560/overview/45acacd5-746b-46ee-8051-d764f929cca3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2586/overview/d9e61ae4-6e56-4f38-9206-5d91ef98c916</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -39871,15 +39921,15 @@
       <c r="J735" t="inlineStr"/>
       <c r="K735" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Wednesday 20 January 2027 11:00am</t>
         </is>
       </c>
       <c r="L735" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46407.45833333334</v>
       </c>
       <c r="M735" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£600,000</t>
         </is>
       </c>
       <c r="N735" s="1" t="n">
@@ -39894,12 +39944,12 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Investor Partnerships – Battery Innovation Programme</t>
+          <t>Sustainable Medicines Manufacturing Innovation: CR&amp;D Round 2</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2595/overview/f2b849f6-0fb3-4012-be1b-a41813c93085</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2560/overview/45acacd5-746b-46ee-8051-d764f929cca3</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -39921,15 +39971,15 @@
       <c r="J736" t="inlineStr"/>
       <c r="K736" t="inlineStr">
         <is>
-          <t>Wednesday 25 November 2026 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L736" s="1" t="n">
-        <v>46351.45833333334</v>
+        <v>46358.45833333334</v>
       </c>
       <c r="M736" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N736" s="1" t="n">
@@ -39944,12 +39994,12 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 12</t>
+          <t>Investor Partnerships – Battery Innovation Programme</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2591/overview/b66dd413-9894-4fc4-a6c9-cced53367568</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2595/overview/f2b849f6-0fb3-4012-be1b-a41813c93085</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -39971,15 +40021,15 @@
       <c r="J737" t="inlineStr"/>
       <c r="K737" t="inlineStr">
         <is>
-          <t>Wednesday 11 November 2026 11:00am</t>
+          <t>Wednesday 25 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L737" s="1" t="n">
-        <v>46337.45833333334</v>
+        <v>46351.45833333334</v>
       </c>
       <c r="M737" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N737" s="1" t="n">
@@ -39994,21 +40044,21 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Operational Systems</t>
+          <t>ADOPT Facilitator Support Grant: Round 12</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2599/overview/1931f35c-87fe-4b6a-a718-a61a2d00e86a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2591/overview/b66dd413-9894-4fc4-a6c9-cced53367568</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2026-10-06 16:27</t>
+          <t>2026-10-05 19:06</t>
         </is>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46301.68541666667</v>
+        <v>46300.79583333333</v>
       </c>
       <c r="F738" t="b">
         <v>1</v>
@@ -40021,15 +40071,15 @@
       <c r="J738" t="inlineStr"/>
       <c r="K738" t="inlineStr">
         <is>
-          <t>Tuesday 8 December 2026 11:00am</t>
+          <t>Wednesday 11 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L738" s="1" t="n">
-        <v>46364.45833333334</v>
+        <v>46337.45833333334</v>
       </c>
       <c r="M738" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N738" s="1" t="n">
@@ -40044,12 +40094,12 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Decision Critical Systems</t>
+          <t>BridgeAI Deployment Catalyst: AI for Operational Systems</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2598/overview/cfb35198-55fc-4aad-afa1-86a260bfaddf</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2599/overview/1931f35c-87fe-4b6a-a718-a61a2d00e86a</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -40094,12 +40144,12 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>BridgeAI Deployment Catalyst: AI for Assurance and Compliance</t>
+          <t>BridgeAI Deployment Catalyst: AI for Decision Critical Systems</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2597/overview/7ec02a95-73e5-4928-8104-67a9f1b279e3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2598/overview/cfb35198-55fc-4aad-afa1-86a260bfaddf</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -40144,21 +40194,21 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>FOAK Builder: Programme Entry Expression of Interest</t>
+          <t>BridgeAI Deployment Catalyst: AI for Assurance and Compliance</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2600/overview/0c422454-a8af-4c24-a74a-565426f42395</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2597/overview/7ec02a95-73e5-4928-8104-67a9f1b279e3</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-06 16:27</t>
         </is>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46302.71527777778</v>
+        <v>46301.68541666667</v>
       </c>
       <c r="F741" t="b">
         <v>1</v>
@@ -40171,19 +40221,19 @@
       <c r="J741" t="inlineStr"/>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Thursday 5 November 2026 11:00am</t>
+          <t>Tuesday 8 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L741" s="1" t="n">
-        <v>46331.45833333334</v>
+        <v>46364.45833333334</v>
       </c>
       <c r="M741" t="inlineStr">
         <is>
-          <t>£100.0 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N741" s="1" t="n">
-        <v>46302</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="742">
@@ -40194,21 +40244,21 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 10</t>
+          <t>FOAK Builder: Programme Entry Expression of Interest</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2596/overview/31f0a768-2a9a-405d-b0a4-83a8c5b395c0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2600/overview/0c422454-a8af-4c24-a74a-565426f42395</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2026-10-08 17:07</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46303.71319444444</v>
+        <v>46302.71527777778</v>
       </c>
       <c r="F742" t="b">
         <v>1</v>
@@ -40221,15 +40271,15 @@
       <c r="J742" t="inlineStr"/>
       <c r="K742" t="inlineStr">
         <is>
-          <t>Wednesday 2 December 2026 11:00am</t>
+          <t>Thursday 5 November 2026 11:00am</t>
         </is>
       </c>
       <c r="L742" s="1" t="n">
-        <v>46358.45833333334</v>
+        <v>46331.45833333334</v>
       </c>
       <c r="M742" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£100.0 million</t>
         </is>
       </c>
       <c r="N742" s="1" t="n">
@@ -40244,21 +40294,21 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Growth Cohorts: Next-gen low carbon concrete cohort entry Round 2</t>
+          <t>Full ADOPT Grant: Round 10</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2602/overview/607351e2-798f-450b-b77d-3131912bcbef</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2596/overview/31f0a768-2a9a-405d-b0a4-83a8c5b395c0</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-08 17:07</t>
         </is>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46309.61805555555</v>
+        <v>46303.71319444444</v>
       </c>
       <c r="F743" t="b">
         <v>1</v>
@@ -40279,11 +40329,11 @@
       </c>
       <c r="M743" t="inlineStr">
         <is>
-          <t>£54,400</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N743" s="1" t="n">
-        <v>46309</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="744">
@@ -40294,21 +40344,21 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 - 2027 Round 4</t>
+          <t>Growth Cohorts: Next-gen low carbon concrete cohort entry Round 2</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2605/overview/4b82d27a-2794-457c-8dc7-7ec4f6911c84</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2602/overview/607351e2-798f-450b-b77d-3131912bcbef</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>2026-10-19 16:45</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46314.69791666666</v>
+        <v>46309.61805555555</v>
       </c>
       <c r="F744" t="b">
         <v>1</v>
@@ -40321,13 +40371,17 @@
       <c r="J744" t="inlineStr"/>
       <c r="K744" t="inlineStr">
         <is>
-          <t>Wednesday 27 January 2027 11:00am</t>
+          <t>Wednesday 2 December 2026 11:00am</t>
         </is>
       </c>
       <c r="L744" s="1" t="n">
-        <v>46414.45833333334</v>
-      </c>
-      <c r="M744" t="inlineStr"/>
+        <v>46358.45833333334</v>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>£54,400</t>
+        </is>
+      </c>
       <c r="N744" s="1" t="n">
         <v>46309</v>
       </c>
@@ -40340,21 +40394,21 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Healthy Soils and Water for a Sustainable Environment</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 - 2027 Round 4</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2605/overview/4b82d27a-2794-457c-8dc7-7ec4f6911c84</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-19 16:45</t>
         </is>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46317.61736111111</v>
+        <v>46314.69791666666</v>
       </c>
       <c r="F745" t="b">
         <v>1</v>
@@ -40367,18 +40421,64 @@
       <c r="J745" t="inlineStr"/>
       <c r="K745" t="inlineStr">
         <is>
+          <t>Wednesday 27 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L745" s="1" t="n">
+        <v>46414.45833333334</v>
+      </c>
+      <c r="M745" t="inlineStr"/>
+      <c r="N745" s="1" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Healthy Soils and Water for a Sustainable Environment</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:49</t>
+        </is>
+      </c>
+      <c r="E746" s="1" t="n">
+        <v>46317.61736111111</v>
+      </c>
+      <c r="F746" t="b">
+        <v>1</v>
+      </c>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="b">
+        <v>0</v>
+      </c>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
           <t>Thursday 28 January 2027 11:00am</t>
         </is>
       </c>
-      <c r="L745" s="1" t="n">
+      <c r="L746" s="1" t="n">
         <v>46415.45833333334</v>
       </c>
-      <c r="M745" t="inlineStr">
+      <c r="M746" t="inlineStr">
         <is>
           <t>£5.0 million</t>
         </is>
       </c>
-      <c r="N745" s="1" t="n">
+      <c r="N746" s="1" t="n">
         <v>46316</v>
       </c>
     </row>
@@ -40420,10 +40520,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3">
@@ -40446,10 +40546,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C4" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,26 +1109,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iX Challenge: Systemic capture and analysis of structural condition data</t>
+          <t>Underground hydrogen storage demonstrator DEVEX support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-systemic-capture-and-analysis-of-structural-condition-data/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2608/overview/edd17e49-cb74-4ae3-89ee-0ceed80c4618</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:41</t>
+          <t>2026-10-26 16:25</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319.57013888889</v>
+        <v>46321.68402777778</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1137,21 +1137,21 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46318</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>Wednesday 13 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46400.45833333334</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>£750,000</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="n">
         <v>46316</v>
       </c>
@@ -1159,26 +1159,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Secure Innovation Security Reviews</t>
+          <t>Testing and validating underground hydrogen storage components</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/secure-innovation-security-review/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2606/overview/52a725a1-ecfe-4eec-a30a-ac6d4078c350</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:29</t>
+          <t>2026-10-26 16:25</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318.60347222222</v>
+        <v>46321.68402777778</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -1187,25 +1187,19 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>23/10/2026</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46318</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31/01/2027                              12:00</t>
+          <t>Wednesday 13 January 2027 11:00am</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46418.5</v>
+        <v>46400.45833333334</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£315,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N3" s="1" t="n">
@@ -1215,26 +1209,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Healthy Soils and Water for a Sustainable Environment</t>
+          <t>iX Challenge: Systemic capture and analysis of structural condition data</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-systemic-capture-and-analysis-of-structural-condition-data/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-24 13:41</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317.61736111111</v>
+        <v>46319.57013888889</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -1243,21 +1237,21 @@
       <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>46318</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Thursday 28 January 2027 11:00am</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>46415.45833333334</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>£5.0 million</t>
-        </is>
-      </c>
+          <t>04/12/2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" s="1" t="n">
         <v>46316</v>
       </c>
@@ -1270,21 +1264,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
+          <t>Secure Innovation Security Reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/secure-innovation-security-review/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-21 14:43</t>
+          <t>2026-10-23 14:29</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316.61319444444</v>
+        <v>46318.60347222222</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1295,21 +1289,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>31/01/2027                              12:00</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>46418.5</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£315,000</t>
         </is>
       </c>
       <c r="N5" s="1" t="n">
@@ -1319,26 +1315,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
+          <t>Healthy Soils and Water for a Sustainable Environment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2604/overview/0a26a044-e3c5-4fa0-8556-b382497374df</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-21 14:43</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316.61319444444</v>
+        <v>46317.61736111111</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -1347,23 +1343,19 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20/10/2026</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>46315</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>Thursday 28 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>46415.45833333334</v>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N6" s="1" t="n">
@@ -1378,12 +1370,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+          <t>ARIA: Standards and benchmarks for dexterous robotics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-standards-and-benchmarks-for-dexterous-robotics/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1403,20 +1395,128 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>£3.0 million</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UK Space Agency: Unlocking Space for Business - Environmental Intelligence and Emissions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/uk-space-agency-unlocking-space-for-business-environmental-intelligence-and-emissions/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:43</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46316.61319444444</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EIT Urban Mobility: SME Market Expansion Open Call 2027</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/eit-urban-mobility-sme-market-expansion-open-call-2027/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:43</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46316.61319444444</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>01/12/2026</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" s="1" t="n">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="1" t="n">
         <v>46316</v>
       </c>
     </row>
@@ -1461,13 +1561,13 @@
         <v>46316</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2475,7 +2575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N746"/>
+  <dimension ref="A1:N748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40479,6 +40579,106 @@
         </is>
       </c>
       <c r="N746" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Underground hydrogen storage demonstrator DEVEX support</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2608/overview/edd17e49-cb74-4ae3-89ee-0ceed80c4618</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:25</t>
+        </is>
+      </c>
+      <c r="E747" s="1" t="n">
+        <v>46321.68402777778</v>
+      </c>
+      <c r="F747" t="b">
+        <v>1</v>
+      </c>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="b">
+        <v>0</v>
+      </c>
+      <c r="I747" t="inlineStr"/>
+      <c r="J747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Wednesday 13 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L747" s="1" t="n">
+        <v>46400.45833333334</v>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>£750,000</t>
+        </is>
+      </c>
+      <c r="N747" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Testing and validating underground hydrogen storage components</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2606/overview/52a725a1-ecfe-4eec-a30a-ac6d4078c350</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:25</t>
+        </is>
+      </c>
+      <c r="E748" s="1" t="n">
+        <v>46321.68402777778</v>
+      </c>
+      <c r="F748" t="b">
+        <v>1</v>
+      </c>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="b">
+        <v>0</v>
+      </c>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Wednesday 13 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L748" s="1" t="n">
+        <v>46400.45833333334</v>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
+      <c r="N748" s="1" t="n">
         <v>46316</v>
       </c>
     </row>
@@ -40533,10 +40733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -40546,10 +40746,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C4" t="n">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
+++ b/outputs/InnovateUK_Funding_Opportunities_Latest.xlsx
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,26 +1221,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovate UK Business Connect</t>
+          <t>Innovate Funding Service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ARIA: TA1 Integrated Robot Bodies and TA2 Foundational Technologies – Concept papers</t>
+          <t>Investor Partnerships - National Materials Innovation Programme 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/aria-ta1-integrated-robot-bodies-and-ta2-foundational-technologies-concept-papers/</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2616/overview/d8e92206-e9dc-43d5-8d52-4fbfbd78339c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:18</t>
+          <t>2026-10-30 16:28</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323.67916666667</v>
+        <v>46325.68611111111</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -1251,11 +1251,17 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tuesday 19 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46406.45833333334</v>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£15</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N2" s="1" t="n">
@@ -1270,12 +1276,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EIT Higher Education Initiative Call for Proposals 2026</t>
+          <t>ARIA: TA1 Integrated Robot Bodies and TA2 Foundational Technologies – Concept papers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://iuk-business-connect.org.uk/opportunities/eit-higher-education-initiative-call-for-proposals-2026/</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/aria-ta1-integrated-robot-bodies-and-ta2-foundational-technologies-concept-papers/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1293,22 +1299,66 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>£15</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EIT Higher Education Initiative Call for Proposals 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/eit-higher-education-initiative-call-for-proposals-2026/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:18</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46323.67916666667</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>20/10/2026</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>46315</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>13/01/2027</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" s="1" t="n">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="1" t="n">
         <v>46323</v>
       </c>
     </row>
@@ -1353,13 +1403,13 @@
         <v>46323</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2381,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N754"/>
+  <dimension ref="A1:N755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40798,6 +40848,56 @@
       </c>
       <c r="N754" s="1" t="n">
         <v>46316</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Investor Partnerships - National Materials Innovation Programme 1</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2616/overview/d8e92206-e9dc-43d5-8d52-4fbfbd78339c</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>2026-10-30 16:28</t>
+        </is>
+      </c>
+      <c r="E755" s="1" t="n">
+        <v>46325.68611111111</v>
+      </c>
+      <c r="F755" t="b">
+        <v>1</v>
+      </c>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="b">
+        <v>0</v>
+      </c>
+      <c r="I755" t="inlineStr"/>
+      <c r="J755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Tuesday 19 January 2027 11:00am</t>
+        </is>
+      </c>
+      <c r="L755" s="1" t="n">
+        <v>46406.45833333334</v>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N755" s="1" t="n">
+        <v>46323</v>
       </c>
     </row>
   </sheetData>
@@ -40851,10 +40951,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -40864,10 +40964,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C4" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5">
